--- a/2026/BRIN 3219/Febrero/BRIN3219-EXPENSAS-Febrero.xlsx
+++ b/2026/BRIN 3219/Febrero/BRIN3219-EXPENSAS-Febrero.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 3219\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 3219\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4EF1DD-9F3B-4AF9-B13E-039D83E3B30B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B019126-13FC-4B4C-8C32-A7160F32D1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="27" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$O$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$96</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$98</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="162">
   <si>
     <t>U.F.</t>
   </si>
@@ -492,24 +492,6 @@
     <t>INGRESO</t>
   </si>
   <si>
-    <t>VTO: 16/02</t>
-  </si>
-  <si>
-    <t>ENERO</t>
-  </si>
-  <si>
-    <t>Damato fumigaciones - ENERO</t>
-  </si>
-  <si>
-    <t>Egresos por gastos mes - ENERO</t>
-  </si>
-  <si>
-    <t>Destapacion AySa</t>
-  </si>
-  <si>
-    <t>Julio Doartero - Cambio de canilla robada</t>
-  </si>
-  <si>
     <t>Lema - Quedaba pendiente de abonar $1.481.119,50 - Se abona $1.310.527,79 : Resta abonar $170.591,71</t>
   </si>
   <si>
@@ -523,6 +505,30 @@
   </si>
   <si>
     <t>Extraordinarias</t>
+  </si>
+  <si>
+    <t>FEBRERO</t>
+  </si>
+  <si>
+    <t>Damato fumigaciones - FEBRERO</t>
+  </si>
+  <si>
+    <t>Egresos por gastos mes - FEBRERO</t>
+  </si>
+  <si>
+    <t>VTO: 13/03</t>
+  </si>
+  <si>
+    <t>Julio Doartero</t>
+  </si>
+  <si>
+    <t>Aboagado</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>Cerrajeria</t>
   </si>
 </sst>
 </file>
@@ -1331,7 +1337,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="245">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1628,12 +1634,105 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="30" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1652,108 +1751,18 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1769,6 +1778,18 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1778,21 +1799,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2239,7 +2247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28.6640625" customWidth="1"/>
@@ -2264,23 +2272,23 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="216"/>
-      <c r="E2" s="217"/>
-      <c r="F2" s="217"/>
-      <c r="G2" s="217"/>
-      <c r="H2" s="218"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="190"/>
+      <c r="F2" s="190"/>
+      <c r="G2" s="190"/>
+      <c r="H2" s="191"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="226">
+      <c r="E3" s="204">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="226"/>
-      <c r="G3" s="226"/>
-      <c r="H3" s="227"/>
+      <c r="F3" s="204"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="205"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10"/>
@@ -2327,10 +2335,10 @@
         <v>66</v>
       </c>
       <c r="F8" s="89" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H8" s="20"/>
     </row>
@@ -2359,14 +2367,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="224"/>
-      <c r="B12" s="187"/>
-      <c r="C12" s="187"/>
-      <c r="D12" s="187"/>
-      <c r="E12" s="187"/>
-      <c r="F12" s="187"/>
-      <c r="G12" s="187"/>
-      <c r="H12" s="225"/>
+      <c r="A12" s="201"/>
+      <c r="B12" s="202"/>
+      <c r="C12" s="202"/>
+      <c r="D12" s="202"/>
+      <c r="E12" s="202"/>
+      <c r="F12" s="202"/>
+      <c r="G12" s="202"/>
+      <c r="H12" s="203"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -2379,16 +2387,16 @@
       <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:9" ht="15.6">
-      <c r="A14" s="198" t="s">
+      <c r="A14" s="206" t="s">
         <v>122</v>
       </c>
-      <c r="B14" s="198"/>
-      <c r="C14" s="198"/>
-      <c r="D14" s="198"/>
-      <c r="E14" s="198"/>
-      <c r="F14" s="198"/>
-      <c r="G14" s="198"/>
-      <c r="H14" s="198"/>
+      <c r="B14" s="206"/>
+      <c r="C14" s="206"/>
+      <c r="D14" s="206"/>
+      <c r="E14" s="206"/>
+      <c r="F14" s="206"/>
+      <c r="G14" s="206"/>
+      <c r="H14" s="206"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="175" t="s">
@@ -2451,16 +2459,16 @@
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" ht="0.75" customHeight="1">
-      <c r="A19" s="220" t="s">
+      <c r="A19" s="197" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="220"/>
-      <c r="C19" s="220"/>
-      <c r="D19" s="220"/>
-      <c r="E19" s="220"/>
-      <c r="F19" s="220"/>
-      <c r="G19" s="220"/>
-      <c r="H19" s="220"/>
+      <c r="B19" s="197"/>
+      <c r="C19" s="197"/>
+      <c r="D19" s="197"/>
+      <c r="E19" s="197"/>
+      <c r="F19" s="197"/>
+      <c r="G19" s="197"/>
+      <c r="H19" s="197"/>
     </row>
     <row r="20" spans="1:9" hidden="1">
       <c r="A20" s="175" t="s">
@@ -2502,16 +2510,16 @@
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="219" t="s">
+      <c r="A23" s="196" t="s">
         <v>127</v>
       </c>
-      <c r="B23" s="219"/>
-      <c r="C23" s="219"/>
-      <c r="D23" s="219"/>
-      <c r="E23" s="219"/>
-      <c r="F23" s="219"/>
-      <c r="G23" s="219"/>
-      <c r="H23" s="219"/>
+      <c r="B23" s="196"/>
+      <c r="C23" s="196"/>
+      <c r="D23" s="196"/>
+      <c r="E23" s="196"/>
+      <c r="F23" s="196"/>
+      <c r="G23" s="196"/>
+      <c r="H23" s="196"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="138" t="s">
@@ -2553,16 +2561,16 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A27" s="199" t="s">
+      <c r="A27" s="192" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="199"/>
-      <c r="C27" s="199"/>
-      <c r="D27" s="199"/>
-      <c r="E27" s="199"/>
-      <c r="F27" s="199"/>
-      <c r="G27" s="199"/>
-      <c r="H27" s="199"/>
+      <c r="B27" s="192"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="192"/>
+      <c r="F27" s="192"/>
+      <c r="G27" s="192"/>
+      <c r="H27" s="192"/>
     </row>
     <row r="28" spans="1:9" hidden="1">
       <c r="A28" s="175"/>
@@ -2584,9 +2592,9 @@
       <c r="E29" s="138"/>
       <c r="F29" s="138"/>
       <c r="G29" s="138"/>
-      <c r="H29" s="73">
-        <f>59104.24+2928.79+26359.09</f>
-        <v>88392.12</v>
+      <c r="H29" s="243">
+        <f>47767.67+1633.39+14700.53</f>
+        <v>64101.59</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -2615,22 +2623,22 @@
       <c r="G31" s="138"/>
       <c r="H31" s="69">
         <f>SUM(H28:H30)</f>
-        <v>88392.12</v>
+        <v>64101.59</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="199" t="s">
+      <c r="A32" s="192" t="s">
         <v>128</v>
       </c>
-      <c r="B32" s="199"/>
-      <c r="C32" s="199"/>
-      <c r="D32" s="199"/>
-      <c r="E32" s="199"/>
-      <c r="F32" s="199"/>
-      <c r="G32" s="199"/>
-      <c r="H32" s="199"/>
-    </row>
-    <row r="33" spans="1:11" ht="14.25" customHeight="1">
+      <c r="B32" s="192"/>
+      <c r="C32" s="192"/>
+      <c r="D32" s="192"/>
+      <c r="E32" s="192"/>
+      <c r="F32" s="192"/>
+      <c r="G32" s="192"/>
+      <c r="H32" s="192"/>
+    </row>
+    <row r="33" spans="1:10" ht="14.25" customHeight="1">
       <c r="A33" s="138" t="s">
         <v>138</v>
       </c>
@@ -2640,11 +2648,11 @@
       <c r="E33" s="138"/>
       <c r="F33" s="138"/>
       <c r="G33" s="138"/>
-      <c r="H33" s="73">
-        <v>1531896.82</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="H33" s="243">
+        <v>1490686.61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="177" t="s">
         <v>98</v>
       </c>
@@ -2654,11 +2662,11 @@
       <c r="E34" s="138"/>
       <c r="F34" s="138"/>
       <c r="G34" s="138"/>
-      <c r="H34" s="73">
-        <v>96402.21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="H34" s="243">
+        <v>30962.32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="138" t="s">
         <v>73</v>
       </c>
@@ -2670,22 +2678,22 @@
       <c r="G35" s="138"/>
       <c r="H35" s="178">
         <f>SUM(H33:H34)</f>
-        <v>1628299.03</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" s="198" t="s">
+        <v>1521648.9300000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="206" t="s">
         <v>129</v>
       </c>
-      <c r="B36" s="198"/>
-      <c r="C36" s="198"/>
-      <c r="D36" s="198"/>
-      <c r="E36" s="198"/>
-      <c r="F36" s="198"/>
-      <c r="G36" s="198"/>
-      <c r="H36" s="198"/>
-    </row>
-    <row r="37" spans="1:11">
+      <c r="B36" s="206"/>
+      <c r="C36" s="206"/>
+      <c r="D36" s="206"/>
+      <c r="E36" s="206"/>
+      <c r="F36" s="206"/>
+      <c r="G36" s="206"/>
+      <c r="H36" s="206"/>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="80" t="s">
         <v>68</v>
       </c>
@@ -2695,13 +2703,13 @@
       <c r="E37" s="138"/>
       <c r="F37" s="138"/>
       <c r="G37" s="138"/>
-      <c r="H37" s="73">
+      <c r="H37" s="243">
         <v>85000</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:10">
       <c r="A38" s="80" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B38" s="138"/>
       <c r="C38" s="138"/>
@@ -2713,11 +2721,11 @@
         <f>385625+924902.79</f>
         <v>1310527.79</v>
       </c>
-      <c r="I38" s="236"/>
-    </row>
-    <row r="39" spans="1:11">
+      <c r="I38" s="186"/>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="80" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B39" s="138"/>
       <c r="C39" s="138"/>
@@ -2730,7 +2738,7 @@
       </c>
       <c r="I39" s="7"/>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:10">
       <c r="A40" s="138" t="s">
         <v>69</v>
       </c>
@@ -2740,13 +2748,13 @@
       <c r="E40" s="138"/>
       <c r="F40" s="138"/>
       <c r="G40" s="138"/>
-      <c r="H40" s="73">
-        <v>22411.599999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="H40" s="243">
+        <v>23351.65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="138" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B41" s="138"/>
       <c r="C41" s="138"/>
@@ -2754,13 +2762,13 @@
       <c r="E41" s="138"/>
       <c r="F41" s="138"/>
       <c r="G41" s="138"/>
-      <c r="H41" s="73">
+      <c r="H41" s="243">
         <v>65000</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:10">
       <c r="A42" s="138" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B42" s="138"/>
       <c r="C42" s="138"/>
@@ -2768,13 +2776,13 @@
       <c r="E42" s="138"/>
       <c r="F42" s="138"/>
       <c r="G42" s="138"/>
-      <c r="H42" s="73">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" s="80" t="s">
-        <v>154</v>
+      <c r="H42" s="243">
+        <v>47200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="138" t="s">
+        <v>160</v>
       </c>
       <c r="B43" s="138"/>
       <c r="C43" s="138"/>
@@ -2782,13 +2790,13 @@
       <c r="E43" s="138"/>
       <c r="F43" s="138"/>
       <c r="G43" s="138"/>
-      <c r="H43" s="73">
-        <v>85000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" s="138" t="s">
-        <v>73</v>
+      <c r="H43" s="243">
+        <v>50700</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="244" t="s">
+        <v>161</v>
       </c>
       <c r="B44" s="138"/>
       <c r="C44" s="138"/>
@@ -2796,26 +2804,27 @@
       <c r="E44" s="138"/>
       <c r="F44" s="138"/>
       <c r="G44" s="138"/>
-      <c r="H44" s="69">
-        <f>SUM(H37:H43)</f>
-        <v>1827939.3900000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" s="198" t="s">
-        <v>130</v>
-      </c>
-      <c r="B45" s="198"/>
-      <c r="C45" s="198"/>
-      <c r="D45" s="198"/>
-      <c r="E45" s="198"/>
-      <c r="F45" s="198"/>
-      <c r="G45" s="198"/>
-      <c r="H45" s="198"/>
-    </row>
-    <row r="46" spans="1:11">
+      <c r="H44" s="243">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="244" t="s">
+        <v>158</v>
+      </c>
+      <c r="B45" s="138"/>
+      <c r="C45" s="138"/>
+      <c r="D45" s="138"/>
+      <c r="E45" s="138"/>
+      <c r="F45" s="138"/>
+      <c r="G45" s="138"/>
+      <c r="H45" s="243">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="138" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B46" s="138"/>
       <c r="C46" s="138"/>
@@ -2823,30 +2832,26 @@
       <c r="E46" s="138"/>
       <c r="F46" s="138"/>
       <c r="G46" s="138"/>
-      <c r="H46" s="73">
-        <v>170100</v>
-      </c>
-      <c r="J46" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
-      <c r="A47" s="138" t="s">
-        <v>115</v>
-      </c>
-      <c r="B47" s="138"/>
-      <c r="C47" s="138"/>
-      <c r="D47" s="138"/>
-      <c r="E47" s="138"/>
-      <c r="F47" s="138"/>
-      <c r="G47" s="138"/>
-      <c r="H47" s="73">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="H46" s="69">
+        <f>SUM(H37:H45)</f>
+        <v>1841779.44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="206" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47" s="206"/>
+      <c r="C47" s="206"/>
+      <c r="D47" s="206"/>
+      <c r="E47" s="206"/>
+      <c r="F47" s="206"/>
+      <c r="G47" s="206"/>
+      <c r="H47" s="206"/>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="138" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B48" s="138"/>
       <c r="C48" s="138"/>
@@ -2854,387 +2859,400 @@
       <c r="E48" s="138"/>
       <c r="F48" s="138"/>
       <c r="G48" s="138"/>
-      <c r="H48" s="178">
-        <f>SUM(H46:H47)</f>
-        <v>205100</v>
-      </c>
-      <c r="K48" s="7"/>
-    </row>
-    <row r="49" spans="1:9" s="6" customFormat="1">
-      <c r="A49" s="200" t="s">
+      <c r="H48" s="73">
+        <v>170100</v>
+      </c>
+      <c r="J48" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="138" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" s="138"/>
+      <c r="C49" s="138"/>
+      <c r="D49" s="138"/>
+      <c r="E49" s="138"/>
+      <c r="F49" s="138"/>
+      <c r="G49" s="138"/>
+      <c r="H49" s="243">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="138" t="s">
+        <v>72</v>
+      </c>
+      <c r="B50" s="138"/>
+      <c r="C50" s="138"/>
+      <c r="D50" s="138"/>
+      <c r="E50" s="138"/>
+      <c r="F50" s="138"/>
+      <c r="G50" s="138"/>
+      <c r="H50" s="178">
+        <f>SUM(H48:H49)</f>
+        <v>215100</v>
+      </c>
+      <c r="K50" s="7"/>
+    </row>
+    <row r="51" spans="1:11" s="6" customFormat="1">
+      <c r="A51" s="207" t="s">
         <v>131</v>
       </c>
-      <c r="B49" s="201"/>
-      <c r="C49" s="201"/>
-      <c r="D49" s="201"/>
-      <c r="E49" s="201"/>
-      <c r="F49" s="201"/>
-      <c r="G49" s="201"/>
-      <c r="H49" s="202"/>
-    </row>
-    <row r="50" spans="1:9" s="6" customFormat="1">
-      <c r="A50" s="80" t="s">
+      <c r="B51" s="208"/>
+      <c r="C51" s="208"/>
+      <c r="D51" s="208"/>
+      <c r="E51" s="208"/>
+      <c r="F51" s="208"/>
+      <c r="G51" s="208"/>
+      <c r="H51" s="209"/>
+    </row>
+    <row r="52" spans="1:11" s="6" customFormat="1">
+      <c r="A52" s="80" t="s">
         <v>117</v>
       </c>
-      <c r="B50" s="80"/>
-      <c r="C50" s="80"/>
-      <c r="D50" s="80"/>
-      <c r="E50" s="80"/>
-      <c r="F50" s="80"/>
-      <c r="G50" s="80"/>
-      <c r="H50" s="73">
+      <c r="B52" s="80"/>
+      <c r="C52" s="80"/>
+      <c r="D52" s="80"/>
+      <c r="E52" s="80"/>
+      <c r="F52" s="80"/>
+      <c r="G52" s="80"/>
+      <c r="H52" s="73">
         <v>24990</v>
       </c>
-      <c r="I50" s="60"/>
-    </row>
-    <row r="51" spans="1:9" s="6" customFormat="1">
-      <c r="A51" s="80" t="s">
+      <c r="I52" s="60"/>
+    </row>
+    <row r="53" spans="1:11" s="6" customFormat="1">
+      <c r="A53" s="80" t="s">
         <v>73</v>
       </c>
-      <c r="B51" s="80"/>
-      <c r="C51" s="80"/>
-      <c r="D51" s="80"/>
-      <c r="E51" s="80"/>
-      <c r="F51" s="80"/>
-      <c r="G51" s="80"/>
-      <c r="H51" s="69">
-        <f>SUM(H50)</f>
-        <v>24990</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" s="6" customFormat="1">
-      <c r="A52" s="198" t="s">
-        <v>132</v>
-      </c>
-      <c r="B52" s="198"/>
-      <c r="C52" s="198"/>
-      <c r="D52" s="198"/>
-      <c r="E52" s="198"/>
-      <c r="F52" s="198"/>
-      <c r="G52" s="198"/>
-      <c r="H52" s="198"/>
-    </row>
-    <row r="53" spans="1:9" s="6" customFormat="1">
-      <c r="A53" s="80"/>
       <c r="B53" s="80"/>
       <c r="C53" s="80"/>
       <c r="D53" s="80"/>
       <c r="E53" s="80"/>
       <c r="F53" s="80"/>
       <c r="G53" s="80"/>
-      <c r="H53" s="73"/>
-    </row>
-    <row r="54" spans="1:9" s="6" customFormat="1">
-      <c r="A54" s="80"/>
-      <c r="B54" s="80"/>
-      <c r="C54" s="80"/>
-      <c r="D54" s="80"/>
-      <c r="E54" s="80"/>
-      <c r="F54" s="80"/>
-      <c r="G54" s="80"/>
-      <c r="H54" s="73"/>
-    </row>
-    <row r="55" spans="1:9" s="6" customFormat="1">
-      <c r="A55" s="174"/>
-      <c r="B55" s="174"/>
-      <c r="C55" s="174"/>
-      <c r="D55" s="174"/>
-      <c r="E55" s="174"/>
-      <c r="F55" s="174"/>
-      <c r="G55" s="174"/>
-      <c r="H55" s="173">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A56" s="80" t="s">
-        <v>74</v>
-      </c>
+      <c r="H53" s="69">
+        <f>SUM(H52)</f>
+        <v>24990</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" s="6" customFormat="1">
+      <c r="A54" s="206" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" s="206"/>
+      <c r="C54" s="206"/>
+      <c r="D54" s="206"/>
+      <c r="E54" s="206"/>
+      <c r="F54" s="206"/>
+      <c r="G54" s="206"/>
+      <c r="H54" s="206"/>
+    </row>
+    <row r="55" spans="1:11" s="6" customFormat="1">
+      <c r="A55" s="244" t="s">
+        <v>159</v>
+      </c>
+      <c r="B55" s="80"/>
+      <c r="C55" s="80"/>
+      <c r="D55" s="80"/>
+      <c r="E55" s="80"/>
+      <c r="F55" s="80"/>
+      <c r="G55" s="80"/>
+      <c r="H55" s="243">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" s="6" customFormat="1">
+      <c r="A56" s="80"/>
       <c r="B56" s="80"/>
       <c r="C56" s="80"/>
       <c r="D56" s="80"/>
       <c r="E56" s="80"/>
       <c r="F56" s="80"/>
       <c r="G56" s="80"/>
-      <c r="H56" s="69">
-        <f>SUM(H53:H55)</f>
-        <v>0</v>
-      </c>
-      <c r="I56" s="60"/>
-    </row>
-    <row r="57" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A57" s="200"/>
-      <c r="B57" s="201"/>
-      <c r="C57" s="201"/>
-      <c r="D57" s="201"/>
-      <c r="E57" s="201"/>
-      <c r="F57" s="201"/>
-      <c r="G57" s="201"/>
-      <c r="H57" s="202"/>
-    </row>
-    <row r="58" spans="1:9" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A58" s="81"/>
-      <c r="B58" s="82"/>
-      <c r="C58" s="82"/>
-      <c r="D58" s="82"/>
-      <c r="E58" s="82"/>
-      <c r="F58" s="82"/>
-      <c r="G58" s="82"/>
-      <c r="H58" s="157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A59" s="158"/>
-      <c r="B59" s="159"/>
-      <c r="C59" s="159"/>
-      <c r="D59" s="159"/>
-      <c r="E59" s="159"/>
-      <c r="F59" s="159"/>
-      <c r="G59" s="159"/>
-      <c r="H59" s="160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A60" s="161"/>
-      <c r="B60" s="162"/>
-      <c r="C60" s="162"/>
-      <c r="D60" s="162"/>
-      <c r="E60" s="162"/>
-      <c r="F60" s="162"/>
-      <c r="G60" s="162"/>
+      <c r="H56" s="73"/>
+    </row>
+    <row r="57" spans="1:11" s="6" customFormat="1">
+      <c r="A57" s="174"/>
+      <c r="B57" s="174"/>
+      <c r="C57" s="174"/>
+      <c r="D57" s="174"/>
+      <c r="E57" s="174"/>
+      <c r="F57" s="174"/>
+      <c r="G57" s="174"/>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A58" s="80" t="s">
+        <v>74</v>
+      </c>
+      <c r="B58" s="80"/>
+      <c r="C58" s="80"/>
+      <c r="D58" s="80"/>
+      <c r="E58" s="80"/>
+      <c r="F58" s="80"/>
+      <c r="G58" s="80"/>
+      <c r="H58" s="69">
+        <f>SUM(H55:H57)</f>
+        <v>100000</v>
+      </c>
+      <c r="I58" s="60"/>
+    </row>
+    <row r="59" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A59" s="207"/>
+      <c r="B59" s="208"/>
+      <c r="C59" s="208"/>
+      <c r="D59" s="208"/>
+      <c r="E59" s="208"/>
+      <c r="F59" s="208"/>
+      <c r="G59" s="208"/>
+      <c r="H59" s="209"/>
+    </row>
+    <row r="60" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
+      <c r="A60" s="81"/>
+      <c r="B60" s="82"/>
+      <c r="C60" s="82"/>
+      <c r="D60" s="82"/>
+      <c r="E60" s="82"/>
+      <c r="F60" s="82"/>
+      <c r="G60" s="82"/>
       <c r="H60" s="157">
-        <f>H58+H59</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A61" s="211" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
+      <c r="A61" s="158"/>
+      <c r="B61" s="159"/>
+      <c r="C61" s="159"/>
+      <c r="D61" s="159"/>
+      <c r="E61" s="159"/>
+      <c r="F61" s="159"/>
+      <c r="G61" s="159"/>
+      <c r="H61" s="160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A62" s="161"/>
+      <c r="B62" s="162"/>
+      <c r="C62" s="162"/>
+      <c r="D62" s="162"/>
+      <c r="E62" s="162"/>
+      <c r="F62" s="162"/>
+      <c r="G62" s="162"/>
+      <c r="H62" s="157">
+        <f>H60+H61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A63" s="213" t="s">
         <v>80</v>
       </c>
-      <c r="B61" s="212"/>
-      <c r="C61" s="212"/>
-      <c r="D61" s="212"/>
-      <c r="E61" s="212"/>
-      <c r="F61" s="212"/>
-      <c r="G61" s="212"/>
-      <c r="H61" s="163">
-        <f>H56</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A62" s="214"/>
-      <c r="B62" s="214"/>
-      <c r="C62" s="214"/>
-      <c r="D62" s="214"/>
-      <c r="E62" s="214"/>
-      <c r="F62" s="214"/>
-      <c r="G62" s="214"/>
-      <c r="H62" s="214"/>
-    </row>
-    <row r="63" spans="1:9" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A63" s="215"/>
-      <c r="B63" s="215"/>
-      <c r="C63" s="215"/>
-      <c r="D63" s="215"/>
-      <c r="E63" s="215"/>
-      <c r="F63" s="215"/>
-      <c r="G63" s="215"/>
-      <c r="H63" s="215"/>
-    </row>
-    <row r="64" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A64" s="213" t="s">
+      <c r="B63" s="214"/>
+      <c r="C63" s="214"/>
+      <c r="D63" s="214"/>
+      <c r="E63" s="214"/>
+      <c r="F63" s="214"/>
+      <c r="G63" s="214"/>
+      <c r="H63" s="163">
+        <f>H58</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A64" s="218"/>
+      <c r="B64" s="218"/>
+      <c r="C64" s="218"/>
+      <c r="D64" s="218"/>
+      <c r="E64" s="218"/>
+      <c r="F64" s="218"/>
+      <c r="G64" s="218"/>
+      <c r="H64" s="218"/>
+    </row>
+    <row r="65" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
+      <c r="A65" s="219"/>
+      <c r="B65" s="219"/>
+      <c r="C65" s="219"/>
+      <c r="D65" s="219"/>
+      <c r="E65" s="219"/>
+      <c r="F65" s="219"/>
+      <c r="G65" s="219"/>
+      <c r="H65" s="219"/>
+    </row>
+    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A66" s="217" t="s">
         <v>82</v>
       </c>
-      <c r="B64" s="213"/>
-      <c r="C64" s="213"/>
-      <c r="D64" s="213"/>
-      <c r="E64" s="213"/>
-      <c r="F64" s="213"/>
-      <c r="G64" s="213"/>
-      <c r="H64" s="164"/>
-    </row>
-    <row r="65" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A65" s="221"/>
-      <c r="B65" s="222"/>
-      <c r="C65" s="222"/>
-      <c r="D65" s="222"/>
-      <c r="E65" s="222"/>
-      <c r="F65" s="222"/>
-      <c r="G65" s="223"/>
-      <c r="H65" s="73"/>
-    </row>
-    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A66" s="128" t="s">
+      <c r="B66" s="217"/>
+      <c r="C66" s="217"/>
+      <c r="D66" s="217"/>
+      <c r="E66" s="217"/>
+      <c r="F66" s="217"/>
+      <c r="G66" s="217"/>
+      <c r="H66" s="164"/>
+    </row>
+    <row r="67" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A67" s="198"/>
+      <c r="B67" s="199"/>
+      <c r="C67" s="199"/>
+      <c r="D67" s="199"/>
+      <c r="E67" s="199"/>
+      <c r="F67" s="199"/>
+      <c r="G67" s="200"/>
+      <c r="H67" s="73"/>
+    </row>
+    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A68" s="128" t="s">
         <v>73</v>
       </c>
-      <c r="B66" s="80"/>
-      <c r="C66" s="80"/>
-      <c r="D66" s="80"/>
-      <c r="E66" s="80"/>
-      <c r="F66" s="80"/>
-      <c r="G66" s="80"/>
-      <c r="H66" s="69">
-        <f>SUM(H65:H65)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A67" s="129"/>
-      <c r="B67" s="129"/>
-      <c r="C67" s="129"/>
-      <c r="D67" s="129"/>
-      <c r="E67" s="129"/>
-      <c r="F67" s="129"/>
-      <c r="G67" s="129"/>
-      <c r="H67" s="130"/>
-    </row>
-    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A68" s="194" t="s">
+      <c r="B68" s="80"/>
+      <c r="C68" s="80"/>
+      <c r="D68" s="80"/>
+      <c r="E68" s="80"/>
+      <c r="F68" s="80"/>
+      <c r="G68" s="80"/>
+      <c r="H68" s="69">
+        <f>SUM(H67:H67)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A69" s="129"/>
+      <c r="B69" s="129"/>
+      <c r="C69" s="129"/>
+      <c r="D69" s="129"/>
+      <c r="E69" s="129"/>
+      <c r="F69" s="129"/>
+      <c r="G69" s="129"/>
+      <c r="H69" s="130"/>
+    </row>
+    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A70" s="215" t="s">
         <v>81</v>
       </c>
-      <c r="B68" s="195"/>
-      <c r="C68" s="195"/>
-      <c r="D68" s="195"/>
-      <c r="E68" s="195"/>
-      <c r="F68" s="195"/>
-      <c r="G68" s="195"/>
-      <c r="H68" s="131">
-        <f>H66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A69" s="206" t="s">
+      <c r="B70" s="216"/>
+      <c r="C70" s="216"/>
+      <c r="D70" s="216"/>
+      <c r="E70" s="216"/>
+      <c r="F70" s="216"/>
+      <c r="G70" s="216"/>
+      <c r="H70" s="131">
+        <f>H68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A71" s="193" t="s">
         <v>87</v>
       </c>
-      <c r="B69" s="207"/>
-      <c r="C69" s="207"/>
-      <c r="D69" s="207"/>
-      <c r="E69" s="207"/>
-      <c r="F69" s="207"/>
-      <c r="G69" s="208"/>
-      <c r="H69" s="131"/>
-    </row>
-    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A70" s="206" t="s">
+      <c r="B71" s="194"/>
+      <c r="C71" s="194"/>
+      <c r="D71" s="194"/>
+      <c r="E71" s="194"/>
+      <c r="F71" s="194"/>
+      <c r="G71" s="195"/>
+      <c r="H71" s="131"/>
+    </row>
+    <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A72" s="193" t="s">
         <v>92</v>
       </c>
-      <c r="B70" s="207"/>
-      <c r="C70" s="207"/>
-      <c r="D70" s="207"/>
-      <c r="E70" s="207"/>
-      <c r="F70" s="207"/>
-      <c r="G70" s="208"/>
-      <c r="H70" s="131">
+      <c r="B72" s="194"/>
+      <c r="C72" s="194"/>
+      <c r="D72" s="194"/>
+      <c r="E72" s="194"/>
+      <c r="F72" s="194"/>
+      <c r="G72" s="195"/>
+      <c r="H72" s="131">
         <v>1000000</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="18">
-      <c r="A71" s="194" t="s">
+    <row r="73" spans="1:11" ht="18">
+      <c r="A73" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="B71" s="195"/>
-      <c r="C71" s="195"/>
-      <c r="D71" s="195"/>
-      <c r="E71" s="195"/>
-      <c r="F71" s="195"/>
-      <c r="G71" s="195"/>
-      <c r="H71" s="131">
-        <f>H26+H35+H44+H48+H51+H31+H18+H22</f>
-        <v>4081947.54</v>
-      </c>
-      <c r="J71" s="172"/>
-      <c r="K71" s="143"/>
-    </row>
-    <row r="72" spans="1:11" ht="18">
-      <c r="A72" s="203" t="s">
+      <c r="B73" s="216"/>
+      <c r="C73" s="216"/>
+      <c r="D73" s="216"/>
+      <c r="E73" s="216"/>
+      <c r="F73" s="216"/>
+      <c r="G73" s="216"/>
+      <c r="H73" s="131">
+        <f>H26+H35+H46+H50+H53+H31+H18+H22</f>
+        <v>3974846.96</v>
+      </c>
+      <c r="J73" s="172"/>
+      <c r="K73" s="143"/>
+    </row>
+    <row r="74" spans="1:11" ht="18">
+      <c r="A74" s="210" t="s">
         <v>120</v>
       </c>
-      <c r="B72" s="204"/>
-      <c r="C72" s="204"/>
-      <c r="D72" s="204"/>
-      <c r="E72" s="204"/>
-      <c r="F72" s="204"/>
-      <c r="G72" s="205"/>
-      <c r="H72" s="132">
-        <f>H69+H71</f>
-        <v>4081947.54</v>
-      </c>
-      <c r="I72" s="127"/>
-      <c r="J72" s="186"/>
-      <c r="K72" s="186"/>
-    </row>
-    <row r="73" spans="1:11" ht="18">
-      <c r="A73" s="203" t="s">
+      <c r="B74" s="211"/>
+      <c r="C74" s="211"/>
+      <c r="D74" s="211"/>
+      <c r="E74" s="211"/>
+      <c r="F74" s="211"/>
+      <c r="G74" s="212"/>
+      <c r="H74" s="132">
+        <f>H71+H73</f>
+        <v>3974846.96</v>
+      </c>
+      <c r="I74" s="127"/>
+      <c r="J74" s="220"/>
+      <c r="K74" s="220"/>
+    </row>
+    <row r="75" spans="1:11" ht="18">
+      <c r="A75" s="210" t="s">
         <v>93</v>
       </c>
-      <c r="B73" s="204"/>
-      <c r="C73" s="204"/>
-      <c r="D73" s="204"/>
-      <c r="E73" s="204"/>
-      <c r="F73" s="204"/>
-      <c r="G73" s="205"/>
-      <c r="H73" s="133">
-        <f>H70+H68</f>
+      <c r="B75" s="211"/>
+      <c r="C75" s="211"/>
+      <c r="D75" s="211"/>
+      <c r="E75" s="211"/>
+      <c r="F75" s="211"/>
+      <c r="G75" s="212"/>
+      <c r="H75" s="133">
+        <f>H72+H70</f>
         <v>1000000</v>
       </c>
-      <c r="J73" s="143"/>
-    </row>
-    <row r="74" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A74" s="209" t="s">
+      <c r="J75" s="143"/>
+    </row>
+    <row r="76" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A76" s="229" t="s">
         <v>83</v>
       </c>
-      <c r="B74" s="210"/>
-      <c r="C74" s="210"/>
-      <c r="D74" s="210"/>
-      <c r="E74" s="210"/>
-      <c r="F74" s="210"/>
-      <c r="G74" s="210"/>
-      <c r="H74" s="134">
-        <f>H71+H68</f>
-        <v>4081947.54</v>
-      </c>
-      <c r="J74" s="7"/>
-    </row>
-    <row r="75" spans="1:11" ht="18" hidden="1">
-      <c r="A75" s="196" t="s">
+      <c r="B76" s="230"/>
+      <c r="C76" s="230"/>
+      <c r="D76" s="230"/>
+      <c r="E76" s="230"/>
+      <c r="F76" s="230"/>
+      <c r="G76" s="230"/>
+      <c r="H76" s="134">
+        <f>H73+H70</f>
+        <v>3974846.96</v>
+      </c>
+      <c r="J76" s="7"/>
+    </row>
+    <row r="77" spans="1:11" ht="18" hidden="1">
+      <c r="A77" s="227" t="s">
         <v>17</v>
       </c>
-      <c r="B75" s="197"/>
-      <c r="C75" s="197"/>
-      <c r="D75" s="197"/>
-      <c r="E75" s="197"/>
-      <c r="F75" s="197"/>
-      <c r="G75" s="197"/>
-      <c r="H75" s="135">
-        <f>H60</f>
-        <v>0</v>
-      </c>
-      <c r="J75" s="7"/>
-    </row>
-    <row r="76" spans="1:11" ht="18" hidden="1">
-      <c r="A76" s="136"/>
-      <c r="B76" s="136"/>
-      <c r="C76" s="136"/>
-      <c r="D76" s="136"/>
-      <c r="E76" s="136"/>
-      <c r="F76" s="136"/>
-      <c r="G76" s="136"/>
-      <c r="H76" s="137"/>
-      <c r="J76" s="7"/>
-    </row>
-    <row r="77" spans="1:11" ht="18" hidden="1">
-      <c r="A77" s="136"/>
-      <c r="B77" s="136"/>
-      <c r="C77" s="136"/>
-      <c r="D77" s="136"/>
-      <c r="E77" s="136"/>
-      <c r="F77" s="136"/>
-      <c r="G77" s="136"/>
-      <c r="H77" s="137"/>
+      <c r="B77" s="228"/>
+      <c r="C77" s="228"/>
+      <c r="D77" s="228"/>
+      <c r="E77" s="228"/>
+      <c r="F77" s="228"/>
+      <c r="G77" s="228"/>
+      <c r="H77" s="135">
+        <f>H62</f>
+        <v>0</v>
+      </c>
       <c r="J77" s="7"/>
     </row>
     <row r="78" spans="1:11" ht="18" hidden="1">
@@ -3248,91 +3266,82 @@
       <c r="H78" s="137"/>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A79" s="138"/>
-      <c r="B79" s="138"/>
-      <c r="C79" s="138"/>
-      <c r="D79" s="138"/>
-      <c r="E79" s="138"/>
-      <c r="F79" s="138"/>
-      <c r="G79" s="138"/>
-      <c r="H79" s="138"/>
-    </row>
-    <row r="80" spans="1:11" ht="18">
-      <c r="A80" s="191" t="s">
+    <row r="79" spans="1:11" ht="18" hidden="1">
+      <c r="A79" s="136"/>
+      <c r="B79" s="136"/>
+      <c r="C79" s="136"/>
+      <c r="D79" s="136"/>
+      <c r="E79" s="136"/>
+      <c r="F79" s="136"/>
+      <c r="G79" s="136"/>
+      <c r="H79" s="137"/>
+      <c r="J79" s="7"/>
+    </row>
+    <row r="80" spans="1:11" ht="18" hidden="1">
+      <c r="A80" s="136"/>
+      <c r="B80" s="136"/>
+      <c r="C80" s="136"/>
+      <c r="D80" s="136"/>
+      <c r="E80" s="136"/>
+      <c r="F80" s="136"/>
+      <c r="G80" s="136"/>
+      <c r="H80" s="137"/>
+      <c r="J80" s="7"/>
+    </row>
+    <row r="81" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A81" s="138"/>
+      <c r="B81" s="138"/>
+      <c r="C81" s="138"/>
+      <c r="D81" s="138"/>
+      <c r="E81" s="138"/>
+      <c r="F81" s="138"/>
+      <c r="G81" s="138"/>
+      <c r="H81" s="138"/>
+    </row>
+    <row r="82" spans="1:11" ht="18">
+      <c r="A82" s="224" t="s">
         <v>10</v>
       </c>
-      <c r="B80" s="192"/>
-      <c r="C80" s="192"/>
-      <c r="D80" s="192"/>
-      <c r="E80" s="192"/>
-      <c r="F80" s="192"/>
-      <c r="G80" s="192"/>
-      <c r="H80" s="193"/>
-    </row>
-    <row r="81" spans="1:11" ht="18">
-      <c r="A81" s="139" t="s">
+      <c r="B82" s="225"/>
+      <c r="C82" s="225"/>
+      <c r="D82" s="225"/>
+      <c r="E82" s="225"/>
+      <c r="F82" s="225"/>
+      <c r="G82" s="225"/>
+      <c r="H82" s="226"/>
+    </row>
+    <row r="83" spans="1:11" ht="18">
+      <c r="A83" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="B81" s="140"/>
-      <c r="C81" s="140"/>
-      <c r="D81" s="140"/>
-      <c r="E81" s="140"/>
-      <c r="F81" s="140"/>
-      <c r="G81" s="140"/>
-      <c r="H81" s="141">
+      <c r="B83" s="140"/>
+      <c r="C83" s="140"/>
+      <c r="D83" s="140"/>
+      <c r="E83" s="140"/>
+      <c r="F83" s="140"/>
+      <c r="G83" s="140"/>
+      <c r="H83" s="141">
         <v>3532612.5527224625</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
-      <c r="A82" s="81" t="s">
-        <v>158</v>
-      </c>
-      <c r="B82" s="82"/>
-      <c r="C82" s="82"/>
-      <c r="D82" s="82"/>
-      <c r="E82" s="82"/>
-      <c r="F82" s="82"/>
-      <c r="G82" s="82"/>
-      <c r="H82" s="142">
+    <row r="84" spans="1:11">
+      <c r="A84" s="81" t="s">
+        <v>152</v>
+      </c>
+      <c r="B84" s="82"/>
+      <c r="C84" s="82"/>
+      <c r="D84" s="82"/>
+      <c r="E84" s="82"/>
+      <c r="F84" s="82"/>
+      <c r="G84" s="82"/>
+      <c r="H84" s="142">
         <f>Planilla!G32</f>
-        <v>3926249.2638619998</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11">
-      <c r="A83" s="78" t="s">
-        <v>152</v>
-      </c>
-      <c r="B83" s="79"/>
-      <c r="C83" s="79"/>
-      <c r="D83" s="79"/>
-      <c r="E83" s="79"/>
-      <c r="F83" s="79"/>
-      <c r="G83" s="79"/>
-      <c r="H83" s="182">
-        <f>-(H74)</f>
-        <v>-4081947.54</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11">
-      <c r="A84" s="78" t="s">
-        <v>84</v>
-      </c>
-      <c r="B84" s="79"/>
-      <c r="C84" s="79"/>
-      <c r="D84" s="79"/>
-      <c r="E84" s="79"/>
-      <c r="F84" s="79"/>
-      <c r="G84" s="79"/>
-      <c r="H84" s="182">
-        <f>-H61</f>
-        <v>0</v>
-      </c>
-      <c r="K84" s="6"/>
+        <v>3936249.2638619998</v>
+      </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="78" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B85" s="79"/>
       <c r="C85" s="79"/>
@@ -3340,13 +3349,14 @@
       <c r="E85" s="79"/>
       <c r="F85" s="79"/>
       <c r="G85" s="79"/>
-      <c r="H85" s="122">
-        <v>133680</v>
+      <c r="H85" s="182">
+        <f>-(H76)</f>
+        <v>-3974846.96</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="78" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B86" s="79"/>
       <c r="C86" s="79"/>
@@ -3354,183 +3364,213 @@
       <c r="E86" s="79"/>
       <c r="F86" s="79"/>
       <c r="G86" s="79"/>
-      <c r="H86" s="122">
+      <c r="H86" s="182">
+        <f>-H63</f>
+        <v>-100000</v>
+      </c>
+      <c r="K86" s="6"/>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="B87" s="79"/>
+      <c r="C87" s="79"/>
+      <c r="D87" s="79"/>
+      <c r="E87" s="79"/>
+      <c r="F87" s="79"/>
+      <c r="G87" s="79"/>
+      <c r="H87" s="122">
+        <v>133680</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="B88" s="79"/>
+      <c r="C88" s="79"/>
+      <c r="D88" s="79"/>
+      <c r="E88" s="79"/>
+      <c r="F88" s="79"/>
+      <c r="G88" s="79"/>
+      <c r="H88" s="122">
         <v>53562.275882499991</v>
       </c>
-      <c r="I86" s="143"/>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="12" t="s">
+      <c r="I88" s="143"/>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B87" s="83"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="98"/>
-    </row>
-    <row r="88" spans="1:11" ht="18">
-      <c r="A88" s="22" t="s">
+      <c r="B89" s="83"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="98"/>
+    </row>
+    <row r="90" spans="1:11" ht="18">
+      <c r="A90" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B88" s="23"/>
-      <c r="C88" s="23"/>
-      <c r="D88" s="23"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="23"/>
-      <c r="G88" s="23"/>
-      <c r="H88" s="84">
-        <f>SUM(H81:H87)</f>
-        <v>3564156.5524669625</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="15" thickBot="1"/>
-    <row r="90" spans="1:11" ht="16.2" thickBot="1">
-      <c r="A90" s="188" t="s">
+      <c r="B90" s="23"/>
+      <c r="C90" s="23"/>
+      <c r="D90" s="23"/>
+      <c r="E90" s="23"/>
+      <c r="F90" s="23"/>
+      <c r="G90" s="23"/>
+      <c r="H90" s="84">
+        <f>SUM(H83:H89)</f>
+        <v>3581257.1324669626</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="15" thickBot="1"/>
+    <row r="92" spans="1:11" ht="16.2" thickBot="1">
+      <c r="A92" s="221" t="s">
         <v>97</v>
       </c>
-      <c r="B90" s="189"/>
-      <c r="C90" s="189"/>
-      <c r="D90" s="189"/>
-      <c r="E90" s="189"/>
-      <c r="F90" s="189"/>
-      <c r="G90" s="189"/>
-      <c r="H90" s="190"/>
-    </row>
-    <row r="91" spans="1:11" ht="15.6">
-      <c r="A91" s="87" t="s">
+      <c r="B92" s="222"/>
+      <c r="C92" s="222"/>
+      <c r="D92" s="222"/>
+      <c r="E92" s="222"/>
+      <c r="F92" s="222"/>
+      <c r="G92" s="222"/>
+      <c r="H92" s="223"/>
+    </row>
+    <row r="93" spans="1:11" ht="15.6">
+      <c r="A93" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="B91" s="87"/>
-      <c r="C91" s="87"/>
-      <c r="D91" s="87"/>
-      <c r="E91" s="87"/>
-      <c r="F91" s="87"/>
-      <c r="G91" s="87"/>
-      <c r="H91" s="88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
-      <c r="A92" s="61" t="s">
+      <c r="B93" s="87"/>
+      <c r="C93" s="87"/>
+      <c r="D93" s="87"/>
+      <c r="E93" s="87"/>
+      <c r="F93" s="87"/>
+      <c r="G93" s="87"/>
+      <c r="H93" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="B92" s="91"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="61"/>
-      <c r="E92" s="61"/>
-      <c r="F92" s="61"/>
-      <c r="G92" s="61"/>
-      <c r="H92" s="126"/>
-    </row>
-    <row r="93" spans="1:11">
-      <c r="A93" s="61"/>
-      <c r="B93" s="97"/>
-      <c r="C93" s="61"/>
-      <c r="D93" s="61"/>
-      <c r="E93" s="61"/>
-      <c r="F93" s="61"/>
-      <c r="G93" s="61"/>
-      <c r="H93" s="21"/>
-    </row>
-    <row r="94" spans="1:11">
-      <c r="A94" s="61"/>
-      <c r="B94" s="61"/>
-      <c r="C94" s="61"/>
+      <c r="B94" s="91"/>
+      <c r="C94" s="4"/>
       <c r="D94" s="61"/>
       <c r="E94" s="61"/>
       <c r="F94" s="61"/>
       <c r="G94" s="61"/>
-      <c r="H94" s="21"/>
+      <c r="H94" s="126"/>
     </row>
     <row r="95" spans="1:11">
-      <c r="A95" s="85" t="s">
+      <c r="A95" s="61"/>
+      <c r="B95" s="97"/>
+      <c r="C95" s="61"/>
+      <c r="D95" s="61"/>
+      <c r="E95" s="61"/>
+      <c r="F95" s="61"/>
+      <c r="G95" s="61"/>
+      <c r="H95" s="21"/>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" s="61"/>
+      <c r="B96" s="61"/>
+      <c r="C96" s="61"/>
+      <c r="D96" s="61"/>
+      <c r="E96" s="61"/>
+      <c r="F96" s="61"/>
+      <c r="G96" s="61"/>
+      <c r="H96" s="21"/>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="B95" s="85"/>
-      <c r="C95" s="85"/>
-      <c r="D95" s="85"/>
-      <c r="E95" s="85"/>
-      <c r="F95" s="85"/>
-      <c r="G95" s="85"/>
-      <c r="H95" s="86">
-        <f>SUM(H91:H94)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" hidden="1">
-      <c r="A98" s="187"/>
-      <c r="B98" s="187"/>
-      <c r="C98" s="187"/>
-      <c r="D98" s="187"/>
-      <c r="E98" s="187"/>
-      <c r="F98" s="187"/>
-      <c r="G98" s="187"/>
-      <c r="H98" s="187"/>
-    </row>
-    <row r="99" spans="1:8" hidden="1">
-      <c r="A99" s="187"/>
-      <c r="B99" s="187"/>
-      <c r="C99" s="187"/>
-      <c r="D99" s="187"/>
-      <c r="E99" s="187"/>
-      <c r="F99" s="187"/>
-      <c r="G99" s="187"/>
-      <c r="H99" s="187"/>
+      <c r="B97" s="85"/>
+      <c r="C97" s="85"/>
+      <c r="D97" s="85"/>
+      <c r="E97" s="85"/>
+      <c r="F97" s="85"/>
+      <c r="G97" s="85"/>
+      <c r="H97" s="86">
+        <f>SUM(H93:H96)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="100" spans="1:8" hidden="1">
-      <c r="A100" s="187"/>
-      <c r="B100" s="187"/>
-      <c r="C100" s="187"/>
-      <c r="D100" s="187"/>
-      <c r="E100" s="187"/>
-      <c r="F100" s="187"/>
-      <c r="G100" s="187"/>
-      <c r="H100" s="187"/>
+      <c r="A100" s="202"/>
+      <c r="B100" s="202"/>
+      <c r="C100" s="202"/>
+      <c r="D100" s="202"/>
+      <c r="E100" s="202"/>
+      <c r="F100" s="202"/>
+      <c r="G100" s="202"/>
+      <c r="H100" s="202"/>
     </row>
     <row r="101" spans="1:8" hidden="1">
-      <c r="A101" s="187"/>
-      <c r="B101" s="187"/>
-      <c r="C101" s="187"/>
-      <c r="D101" s="187"/>
-      <c r="E101" s="187"/>
-      <c r="F101" s="187"/>
-      <c r="G101" s="187"/>
-      <c r="H101" s="187"/>
+      <c r="A101" s="202"/>
+      <c r="B101" s="202"/>
+      <c r="C101" s="202"/>
+      <c r="D101" s="202"/>
+      <c r="E101" s="202"/>
+      <c r="F101" s="202"/>
+      <c r="G101" s="202"/>
+      <c r="H101" s="202"/>
+    </row>
+    <row r="102" spans="1:8" hidden="1">
+      <c r="A102" s="202"/>
+      <c r="B102" s="202"/>
+      <c r="C102" s="202"/>
+      <c r="D102" s="202"/>
+      <c r="E102" s="202"/>
+      <c r="F102" s="202"/>
+      <c r="G102" s="202"/>
+      <c r="H102" s="202"/>
+    </row>
+    <row r="103" spans="1:8" hidden="1">
+      <c r="A103" s="202"/>
+      <c r="B103" s="202"/>
+      <c r="C103" s="202"/>
+      <c r="D103" s="202"/>
+      <c r="E103" s="202"/>
+      <c r="F103" s="202"/>
+      <c r="G103" s="202"/>
+      <c r="H103" s="202"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="A100:H103"/>
+    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A82:H82"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A64:H65"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A72:G72"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A67:G67"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="E3:H3"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A61:G61"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A64:G64"/>
-    <mergeCell ref="A62:H63"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A59:H59"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="J72:K72"/>
-    <mergeCell ref="A98:H101"/>
-    <mergeCell ref="A90:H90"/>
-    <mergeCell ref="A80:H80"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A51:H51"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3571,12 +3611,12 @@
       </c>
       <c r="F1" s="105" t="str">
         <f>RESUMEN!F8</f>
-        <v>ENERO</v>
+        <v>FEBRERO</v>
       </c>
       <c r="G1" s="106"/>
       <c r="H1" s="104" t="str">
         <f>RESUMEN!G8</f>
-        <v>VTO: 16/02</v>
+        <v>VTO: 13/03</v>
       </c>
       <c r="I1" s="103"/>
       <c r="J1" s="103"/>
@@ -3651,16 +3691,16 @@
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="120"/>
-      <c r="B5" s="229">
+      <c r="B5" s="232">
         <f>C3-B7</f>
         <v>2771419.75</v>
       </c>
-      <c r="C5" s="229"/>
+      <c r="C5" s="232"/>
       <c r="D5" s="21"/>
-      <c r="E5" s="239">
+      <c r="E5" s="238">
         <v>70000</v>
       </c>
-      <c r="F5" s="240"/>
+      <c r="F5" s="239"/>
       <c r="G5" s="114"/>
       <c r="H5" s="114"/>
       <c r="I5" s="114"/>
@@ -3673,15 +3713,15 @@
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="120"/>
-      <c r="B6" s="231" t="s">
+      <c r="B6" s="234" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="232"/>
+      <c r="C6" s="235"/>
       <c r="D6" s="21"/>
-      <c r="E6" s="231" t="s">
-        <v>159</v>
-      </c>
-      <c r="F6" s="232"/>
+      <c r="E6" s="234" t="s">
+        <v>153</v>
+      </c>
+      <c r="F6" s="235"/>
       <c r="G6" s="114"/>
       <c r="H6" s="114"/>
       <c r="I6" s="114"/>
@@ -3694,16 +3734,16 @@
     </row>
     <row r="7" spans="1:17" ht="18.75" customHeight="1">
       <c r="A7" s="120"/>
-      <c r="B7" s="229">
+      <c r="B7" s="232">
         <f>C2</f>
         <v>1310527.79</v>
       </c>
-      <c r="C7" s="229"/>
+      <c r="C7" s="232"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="237">
+      <c r="E7" s="236">
         <v>1000000</v>
       </c>
-      <c r="F7" s="238"/>
+      <c r="F7" s="237"/>
       <c r="G7" s="114"/>
       <c r="H7" s="114"/>
       <c r="I7" s="114"/>
@@ -3812,7 +3852,7 @@
         <f>B$7*E9</f>
         <v>53076.375495</v>
       </c>
-      <c r="O9" s="241">
+      <c r="O9" s="187">
         <f>H9+I9-J9+K9+M9+N9+L9</f>
         <v>205818.87537000002</v>
       </c>
@@ -3866,7 +3906,7 @@
         <f t="shared" ref="N10:N31" si="5">B$7*E10</f>
         <v>84922.200792000003</v>
       </c>
-      <c r="O10" s="241">
+      <c r="O10" s="187">
         <f t="shared" ref="O10:O31" si="6">H10+I10-J10+K10+M10+N10+L10</f>
         <v>329310.20059199998</v>
       </c>
@@ -3922,7 +3962,7 @@
         <f t="shared" si="5"/>
         <v>63167.439478</v>
       </c>
-      <c r="O11" s="241">
+      <c r="O11" s="187">
         <f t="shared" si="6"/>
         <v>244949.87142799998</v>
       </c>
@@ -3975,7 +4015,7 @@
         <f t="shared" si="5"/>
         <v>70113.236764999994</v>
       </c>
-      <c r="O12" s="242">
+      <c r="O12" s="188">
         <f t="shared" si="6"/>
         <v>4107987.7727756742</v>
       </c>
@@ -4029,7 +4069,7 @@
         <f t="shared" si="5"/>
         <v>50455.319915</v>
       </c>
-      <c r="O13" s="241">
+      <c r="O13" s="187">
         <f t="shared" si="6"/>
         <v>195654.98028999998</v>
       </c>
@@ -4085,7 +4125,7 @@
         <f t="shared" si="5"/>
         <v>47047.947661000006</v>
       </c>
-      <c r="O14" s="241">
+      <c r="O14" s="187">
         <f t="shared" si="6"/>
         <v>182441.91668600001</v>
       </c>
@@ -4140,7 +4180,7 @@
       <c r="N15" s="25">
         <v>0</v>
       </c>
-      <c r="O15" s="241">
+      <c r="O15" s="187">
         <f t="shared" si="6"/>
         <v>156136.77765</v>
       </c>
@@ -4197,7 +4237,7 @@
         <f t="shared" si="5"/>
         <v>70113.236764999994</v>
       </c>
-      <c r="O16" s="241">
+      <c r="O16" s="187">
         <f t="shared" si="6"/>
         <v>271884.19338999997</v>
       </c>
@@ -4254,7 +4294,7 @@
         <f t="shared" si="5"/>
         <v>50455.319915</v>
       </c>
-      <c r="O17" s="241">
+      <c r="O17" s="187">
         <f t="shared" si="6"/>
         <v>195654.98028999998</v>
       </c>
@@ -4278,16 +4318,16 @@
         <v>318869.51383709081</v>
       </c>
       <c r="G18" s="179">
-        <f>RESUMEN!H47+RESUMEN!H37+RESUMEN!H41</f>
-        <v>185000</v>
+        <f>RESUMEN!H49+RESUMEN!H37+RESUMEN!H41</f>
+        <v>195000</v>
       </c>
       <c r="H18" s="68">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
-        <v>133869.51383709081</v>
+        <v>123869.51383709081</v>
       </c>
       <c r="I18" s="68">
         <f t="shared" si="7"/>
-        <v>4953.1720119723605</v>
+        <v>4583.1720119723605</v>
       </c>
       <c r="J18" s="68">
         <f t="shared" si="1"/>
@@ -4309,9 +4349,9 @@
         <f t="shared" si="5"/>
         <v>47047.947661000006</v>
       </c>
-      <c r="O18" s="241">
+      <c r="O18" s="187">
         <f t="shared" si="6"/>
-        <v>321264.60253506317</v>
+        <v>310894.60253506317</v>
       </c>
       <c r="Q18" s="183"/>
     </row>
@@ -4363,7 +4403,7 @@
         <f t="shared" si="5"/>
         <v>54255.850506000002</v>
       </c>
-      <c r="O19" s="242">
+      <c r="O19" s="188">
         <f t="shared" si="6"/>
         <v>2865140.14929508</v>
       </c>
@@ -4420,7 +4460,7 @@
         <f t="shared" si="5"/>
         <v>70113.236764999994</v>
       </c>
-      <c r="O20" s="241">
+      <c r="O20" s="187">
         <f t="shared" si="6"/>
         <v>271884.19338999997</v>
       </c>
@@ -4476,7 +4516,7 @@
         <f t="shared" si="5"/>
         <v>50455.319915</v>
       </c>
-      <c r="O21" s="242">
+      <c r="O21" s="188">
         <f t="shared" si="6"/>
         <v>1289888.3046149821</v>
       </c>
@@ -4533,7 +4573,7 @@
         <f t="shared" si="5"/>
         <v>47047.947661000006</v>
       </c>
-      <c r="O22" s="241">
+      <c r="O22" s="187">
         <f t="shared" si="6"/>
         <v>182441.91668600001</v>
       </c>
@@ -4590,7 +4630,7 @@
         <f t="shared" si="5"/>
         <v>54255.850506000002</v>
       </c>
-      <c r="O23" s="241">
+      <c r="O23" s="187">
         <f t="shared" si="6"/>
         <v>210392.62815599999</v>
       </c>
@@ -4645,7 +4685,7 @@
         <f t="shared" si="5"/>
         <v>70113.236764999994</v>
       </c>
-      <c r="O24" s="241">
+      <c r="O24" s="187">
         <f t="shared" si="6"/>
         <v>271884.19338999997</v>
       </c>
@@ -4702,7 +4742,7 @@
         <f t="shared" si="5"/>
         <v>50455.319915</v>
       </c>
-      <c r="O25" s="241">
+      <c r="O25" s="187">
         <f t="shared" si="6"/>
         <v>195654.98028999998</v>
       </c>
@@ -4757,7 +4797,7 @@
         <f t="shared" si="5"/>
         <v>47047.947661000006</v>
       </c>
-      <c r="O26" s="241">
+      <c r="O26" s="187">
         <f t="shared" si="6"/>
         <v>182441.91668600001</v>
       </c>
@@ -4813,7 +4853,7 @@
         <f t="shared" si="5"/>
         <v>54255.850506000002</v>
       </c>
-      <c r="O27" s="242">
+      <c r="O27" s="188">
         <f t="shared" si="6"/>
         <v>3164645.4340123115</v>
       </c>
@@ -4865,7 +4905,7 @@
         <f t="shared" si="5"/>
         <v>70113.236764999994</v>
       </c>
-      <c r="O28" s="241">
+      <c r="O28" s="187">
         <f t="shared" si="6"/>
         <v>1993193.5786160715</v>
       </c>
@@ -4920,7 +4960,7 @@
         <f t="shared" si="5"/>
         <v>50455.319915</v>
       </c>
-      <c r="O29" s="241">
+      <c r="O29" s="187">
         <f t="shared" si="6"/>
         <v>195654.98028999998</v>
       </c>
@@ -4984,7 +5024,7 @@
         <f t="shared" si="5"/>
         <v>47047.947661000006</v>
       </c>
-      <c r="O30" s="241">
+      <c r="O30" s="187">
         <f t="shared" si="6"/>
         <v>182441.91668600001</v>
       </c>
@@ -5038,7 +5078,7 @@
         <f t="shared" si="5"/>
         <v>54255.850506000002</v>
       </c>
-      <c r="O31" s="241">
+      <c r="O31" s="187">
         <f t="shared" si="6"/>
         <v>210392.62815599999</v>
       </c>
@@ -5061,15 +5101,15 @@
       </c>
       <c r="G32" s="99">
         <f>SUM(G9:G31)</f>
-        <v>3926249.2638619998</v>
+        <v>3936249.2638619998</v>
       </c>
       <c r="H32" s="123">
         <f>SUM(H9:H31)</f>
-        <v>11957058.150222933</v>
+        <v>11947058.150222933</v>
       </c>
       <c r="I32" s="54">
         <f>SUM(I9:I31)</f>
-        <v>442411.15155824862</v>
+        <v>442041.15155824862</v>
       </c>
       <c r="J32" s="99">
         <f t="shared" ref="J32" si="8">SUM(J9:J31)</f>
@@ -5090,124 +5130,124 @@
       </c>
       <c r="O32" s="54">
         <f>SUM(O9:O31)</f>
-        <v>17427160.99127518</v>
+        <v>17416790.99127518</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:15" hidden="1">
-      <c r="B34" s="228"/>
-      <c r="C34" s="228"/>
-      <c r="D34" s="228"/>
-      <c r="E34" s="228"/>
-      <c r="F34" s="228"/>
-      <c r="G34" s="228"/>
-      <c r="H34" s="228"/>
-      <c r="I34" s="228"/>
-      <c r="J34" s="228"/>
-      <c r="K34" s="228"/>
-      <c r="L34" s="228"/>
-      <c r="M34" s="228"/>
-      <c r="N34" s="228"/>
-      <c r="O34" s="228"/>
+      <c r="B34" s="231"/>
+      <c r="C34" s="231"/>
+      <c r="D34" s="231"/>
+      <c r="E34" s="231"/>
+      <c r="F34" s="231"/>
+      <c r="G34" s="231"/>
+      <c r="H34" s="231"/>
+      <c r="I34" s="231"/>
+      <c r="J34" s="231"/>
+      <c r="K34" s="231"/>
+      <c r="L34" s="231"/>
+      <c r="M34" s="231"/>
+      <c r="N34" s="231"/>
+      <c r="O34" s="231"/>
     </row>
     <row r="35" spans="1:15" hidden="1">
-      <c r="B35" s="228"/>
-      <c r="C35" s="228"/>
-      <c r="D35" s="228"/>
-      <c r="E35" s="228"/>
-      <c r="F35" s="228"/>
-      <c r="G35" s="228"/>
-      <c r="H35" s="228"/>
-      <c r="I35" s="228"/>
-      <c r="J35" s="228"/>
-      <c r="K35" s="228"/>
-      <c r="L35" s="228"/>
-      <c r="M35" s="228"/>
-      <c r="N35" s="228"/>
-      <c r="O35" s="228"/>
+      <c r="B35" s="231"/>
+      <c r="C35" s="231"/>
+      <c r="D35" s="231"/>
+      <c r="E35" s="231"/>
+      <c r="F35" s="231"/>
+      <c r="G35" s="231"/>
+      <c r="H35" s="231"/>
+      <c r="I35" s="231"/>
+      <c r="J35" s="231"/>
+      <c r="K35" s="231"/>
+      <c r="L35" s="231"/>
+      <c r="M35" s="231"/>
+      <c r="N35" s="231"/>
+      <c r="O35" s="231"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
-      <c r="B36" s="228"/>
-      <c r="C36" s="228"/>
-      <c r="D36" s="228"/>
-      <c r="E36" s="228"/>
-      <c r="F36" s="228"/>
-      <c r="G36" s="228"/>
-      <c r="H36" s="228"/>
-      <c r="I36" s="228"/>
-      <c r="J36" s="228"/>
-      <c r="K36" s="228"/>
-      <c r="L36" s="228"/>
-      <c r="M36" s="228"/>
-      <c r="N36" s="228"/>
-      <c r="O36" s="228"/>
+      <c r="B36" s="231"/>
+      <c r="C36" s="231"/>
+      <c r="D36" s="231"/>
+      <c r="E36" s="231"/>
+      <c r="F36" s="231"/>
+      <c r="G36" s="231"/>
+      <c r="H36" s="231"/>
+      <c r="I36" s="231"/>
+      <c r="J36" s="231"/>
+      <c r="K36" s="231"/>
+      <c r="L36" s="231"/>
+      <c r="M36" s="231"/>
+      <c r="N36" s="231"/>
+      <c r="O36" s="231"/>
     </row>
     <row r="37" spans="1:15" hidden="1">
-      <c r="B37" s="228"/>
-      <c r="C37" s="228"/>
-      <c r="D37" s="228"/>
-      <c r="E37" s="228"/>
-      <c r="F37" s="228"/>
-      <c r="G37" s="228"/>
-      <c r="H37" s="228"/>
-      <c r="I37" s="228"/>
-      <c r="J37" s="228"/>
-      <c r="K37" s="228"/>
-      <c r="L37" s="228"/>
-      <c r="M37" s="228"/>
-      <c r="N37" s="228"/>
-      <c r="O37" s="228"/>
+      <c r="B37" s="231"/>
+      <c r="C37" s="231"/>
+      <c r="D37" s="231"/>
+      <c r="E37" s="231"/>
+      <c r="F37" s="231"/>
+      <c r="G37" s="231"/>
+      <c r="H37" s="231"/>
+      <c r="I37" s="231"/>
+      <c r="J37" s="231"/>
+      <c r="K37" s="231"/>
+      <c r="L37" s="231"/>
+      <c r="M37" s="231"/>
+      <c r="N37" s="231"/>
+      <c r="O37" s="231"/>
     </row>
     <row r="38" spans="1:15" hidden="1">
-      <c r="A38" s="230"/>
-      <c r="B38" s="230"/>
-      <c r="C38" s="230"/>
-      <c r="D38" s="230"/>
-      <c r="E38" s="230"/>
-      <c r="F38" s="230"/>
-      <c r="G38" s="230"/>
-      <c r="H38" s="230"/>
-      <c r="I38" s="230"/>
-      <c r="J38" s="230"/>
-      <c r="K38" s="230"/>
-      <c r="L38" s="230"/>
-      <c r="M38" s="230"/>
-      <c r="N38" s="230"/>
-      <c r="O38" s="230"/>
+      <c r="A38" s="233"/>
+      <c r="B38" s="233"/>
+      <c r="C38" s="233"/>
+      <c r="D38" s="233"/>
+      <c r="E38" s="233"/>
+      <c r="F38" s="233"/>
+      <c r="G38" s="233"/>
+      <c r="H38" s="233"/>
+      <c r="I38" s="233"/>
+      <c r="J38" s="233"/>
+      <c r="K38" s="233"/>
+      <c r="L38" s="233"/>
+      <c r="M38" s="233"/>
+      <c r="N38" s="233"/>
+      <c r="O38" s="233"/>
     </row>
     <row r="39" spans="1:15" hidden="1">
-      <c r="A39" s="230"/>
-      <c r="B39" s="230"/>
-      <c r="C39" s="230"/>
-      <c r="D39" s="230"/>
-      <c r="E39" s="230"/>
-      <c r="F39" s="230"/>
-      <c r="G39" s="230"/>
-      <c r="H39" s="230"/>
-      <c r="I39" s="230"/>
-      <c r="J39" s="230"/>
-      <c r="K39" s="230"/>
-      <c r="L39" s="230"/>
-      <c r="M39" s="230"/>
-      <c r="N39" s="230"/>
-      <c r="O39" s="230"/>
+      <c r="A39" s="233"/>
+      <c r="B39" s="233"/>
+      <c r="C39" s="233"/>
+      <c r="D39" s="233"/>
+      <c r="E39" s="233"/>
+      <c r="F39" s="233"/>
+      <c r="G39" s="233"/>
+      <c r="H39" s="233"/>
+      <c r="I39" s="233"/>
+      <c r="J39" s="233"/>
+      <c r="K39" s="233"/>
+      <c r="L39" s="233"/>
+      <c r="M39" s="233"/>
+      <c r="N39" s="233"/>
+      <c r="O39" s="233"/>
     </row>
     <row r="40" spans="1:15" hidden="1">
-      <c r="A40" s="230"/>
-      <c r="B40" s="230"/>
-      <c r="C40" s="230"/>
-      <c r="D40" s="230"/>
-      <c r="E40" s="230"/>
-      <c r="F40" s="230"/>
-      <c r="G40" s="230"/>
-      <c r="H40" s="230"/>
-      <c r="I40" s="230"/>
-      <c r="J40" s="230"/>
-      <c r="K40" s="230"/>
-      <c r="L40" s="230"/>
-      <c r="M40" s="230"/>
-      <c r="N40" s="230"/>
-      <c r="O40" s="230"/>
+      <c r="A40" s="233"/>
+      <c r="B40" s="233"/>
+      <c r="C40" s="233"/>
+      <c r="D40" s="233"/>
+      <c r="E40" s="233"/>
+      <c r="F40" s="233"/>
+      <c r="G40" s="233"/>
+      <c r="H40" s="233"/>
+      <c r="I40" s="233"/>
+      <c r="J40" s="233"/>
+      <c r="K40" s="233"/>
+      <c r="L40" s="233"/>
+      <c r="M40" s="233"/>
+      <c r="N40" s="233"/>
+      <c r="O40" s="233"/>
     </row>
     <row r="41" spans="1:15">
       <c r="O41" s="7"/>
@@ -5242,15 +5282,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="233" t="s">
+      <c r="A1" s="240" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="234"/>
-      <c r="C1" s="234"/>
-      <c r="D1" s="234"/>
-      <c r="E1" s="234"/>
-      <c r="F1" s="234"/>
-      <c r="G1" s="235"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="242"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>

--- a/2026/BRIN 3219/Febrero/BRIN3219-EXPENSAS-Febrero.xlsx
+++ b/2026/BRIN 3219/Febrero/BRIN3219-EXPENSAS-Febrero.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 3219\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 3219\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B019126-13FC-4B4C-8C32-A7160F32D1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13701C8B-5E9A-45D7-B394-6FC909A9D0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="27" r:id="rId1"/>
@@ -26,6 +26,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -492,9 +495,6 @@
     <t>INGRESO</t>
   </si>
   <si>
-    <t>Lema - Quedaba pendiente de abonar $1.481.119,50 - Se abona $1.310.527,79 : Resta abonar $170.591,71</t>
-  </si>
-  <si>
     <t>Nico Plagas - Desratizacion</t>
   </si>
   <si>
@@ -519,16 +519,19 @@
     <t>VTO: 13/03</t>
   </si>
   <si>
-    <t>Julio Doartero</t>
-  </si>
-  <si>
-    <t>Aboagado</t>
-  </si>
-  <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>Cerrajeria</t>
+    <t>Sr. Abogado - Escrito para volver a solicitar la activacion de la cuenta bancaria</t>
+  </si>
+  <si>
+    <t>Copia de llaves - Cerrajeria</t>
+  </si>
+  <si>
+    <t>Lema -Saldo restante a abonar mes anterior (Leer expensas anteriores)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julio Doartero - Cambio de contactora de bomba - Material y mano de obra </t>
   </si>
 </sst>
 </file>
@@ -1337,7 +1340,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1619,8 +1622,6 @@
     </xf>
     <xf numFmtId="164" fontId="17" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1637,6 +1638,81 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1649,15 +1725,6 @@
     <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1676,9 +1743,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1700,69 +1764,6 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1799,8 +1800,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2248,16 +2247,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K103"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2272,23 +2271,23 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="189"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="191"/>
+      <c r="D2" s="212"/>
+      <c r="E2" s="213"/>
+      <c r="F2" s="213"/>
+      <c r="G2" s="213"/>
+      <c r="H2" s="214"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="204">
+      <c r="E3" s="223">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="204"/>
-      <c r="G3" s="204"/>
-      <c r="H3" s="205"/>
+      <c r="F3" s="223"/>
+      <c r="G3" s="223"/>
+      <c r="H3" s="224"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10"/>
@@ -2324,7 +2323,7 @@
       <c r="A7" s="10"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="18">
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="18.75">
       <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
@@ -2335,10 +2334,10 @@
         <v>66</v>
       </c>
       <c r="F8" s="89" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H8" s="20"/>
     </row>
@@ -2367,14 +2366,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="201"/>
-      <c r="B12" s="202"/>
-      <c r="C12" s="202"/>
-      <c r="D12" s="202"/>
-      <c r="E12" s="202"/>
-      <c r="F12" s="202"/>
-      <c r="G12" s="202"/>
-      <c r="H12" s="203"/>
+      <c r="A12" s="221"/>
+      <c r="B12" s="188"/>
+      <c r="C12" s="188"/>
+      <c r="D12" s="188"/>
+      <c r="E12" s="188"/>
+      <c r="F12" s="188"/>
+      <c r="G12" s="188"/>
+      <c r="H12" s="222"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -2386,20 +2385,20 @@
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:9" ht="15.6">
-      <c r="A14" s="206" t="s">
+    <row r="14" spans="1:9" ht="15.75">
+      <c r="A14" s="225" t="s">
         <v>122</v>
       </c>
-      <c r="B14" s="206"/>
-      <c r="C14" s="206"/>
-      <c r="D14" s="206"/>
-      <c r="E14" s="206"/>
-      <c r="F14" s="206"/>
-      <c r="G14" s="206"/>
-      <c r="H14" s="206"/>
+      <c r="B14" s="225"/>
+      <c r="C14" s="225"/>
+      <c r="D14" s="225"/>
+      <c r="E14" s="225"/>
+      <c r="F14" s="225"/>
+      <c r="G14" s="225"/>
+      <c r="H14" s="225"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="175" t="s">
+      <c r="A15" s="173" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="138"/>
@@ -2409,11 +2408,11 @@
       <c r="F15" s="138"/>
       <c r="G15" s="138"/>
       <c r="H15" s="73">
-        <v>326678.40000000002</v>
+        <v>332232.59999999998</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="175" t="s">
+      <c r="A16" s="173" t="s">
         <v>85</v>
       </c>
       <c r="B16" s="138"/>
@@ -2423,12 +2422,12 @@
       <c r="F16" s="138"/>
       <c r="G16" s="138"/>
       <c r="H16" s="73">
-        <v>-51451.839999999997</v>
+        <v>-52326.64</v>
       </c>
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="175" t="s">
+      <c r="A17" s="173" t="s">
         <v>116</v>
       </c>
       <c r="B17" s="138"/>
@@ -2438,12 +2437,12 @@
       <c r="F17" s="138"/>
       <c r="G17" s="138"/>
       <c r="H17" s="73">
-        <v>0.44</v>
+        <v>0.04</v>
       </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="175" t="s">
+      <c r="A18" s="173" t="s">
         <v>73</v>
       </c>
       <c r="B18" s="138"/>
@@ -2454,24 +2453,24 @@
       <c r="G18" s="138"/>
       <c r="H18" s="69">
         <f>SUM(H15:H17)</f>
-        <v>275227.00000000006</v>
+        <v>279905.99999999994</v>
       </c>
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" ht="0.75" customHeight="1">
-      <c r="A19" s="197" t="s">
+      <c r="A19" s="217" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="197"/>
-      <c r="C19" s="197"/>
-      <c r="D19" s="197"/>
-      <c r="E19" s="197"/>
-      <c r="F19" s="197"/>
-      <c r="G19" s="197"/>
-      <c r="H19" s="197"/>
+      <c r="B19" s="217"/>
+      <c r="C19" s="217"/>
+      <c r="D19" s="217"/>
+      <c r="E19" s="217"/>
+      <c r="F19" s="217"/>
+      <c r="G19" s="217"/>
+      <c r="H19" s="217"/>
     </row>
     <row r="20" spans="1:9" hidden="1">
-      <c r="A20" s="175" t="s">
+      <c r="A20" s="173" t="s">
         <v>143</v>
       </c>
       <c r="B20" s="138"/>
@@ -2483,7 +2482,7 @@
       <c r="H20" s="73"/>
     </row>
     <row r="21" spans="1:9" hidden="1">
-      <c r="A21" s="175" t="s">
+      <c r="A21" s="173" t="s">
         <v>144</v>
       </c>
       <c r="B21" s="138"/>
@@ -2495,7 +2494,7 @@
       <c r="H21" s="73"/>
     </row>
     <row r="22" spans="1:9" hidden="1">
-      <c r="A22" s="175" t="s">
+      <c r="A22" s="173" t="s">
         <v>73</v>
       </c>
       <c r="B22" s="138"/>
@@ -2510,16 +2509,16 @@
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="196" t="s">
+      <c r="A23" s="216" t="s">
         <v>127</v>
       </c>
-      <c r="B23" s="196"/>
-      <c r="C23" s="196"/>
-      <c r="D23" s="196"/>
-      <c r="E23" s="196"/>
-      <c r="F23" s="196"/>
-      <c r="G23" s="196"/>
-      <c r="H23" s="196"/>
+      <c r="B23" s="216"/>
+      <c r="C23" s="216"/>
+      <c r="D23" s="216"/>
+      <c r="E23" s="216"/>
+      <c r="F23" s="216"/>
+      <c r="G23" s="216"/>
+      <c r="H23" s="216"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="138" t="s">
@@ -2561,19 +2560,19 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A27" s="192" t="s">
+      <c r="A27" s="215" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="192"/>
-      <c r="C27" s="192"/>
-      <c r="D27" s="192"/>
-      <c r="E27" s="192"/>
-      <c r="F27" s="192"/>
-      <c r="G27" s="192"/>
-      <c r="H27" s="192"/>
+      <c r="B27" s="215"/>
+      <c r="C27" s="215"/>
+      <c r="D27" s="215"/>
+      <c r="E27" s="215"/>
+      <c r="F27" s="215"/>
+      <c r="G27" s="215"/>
+      <c r="H27" s="215"/>
     </row>
     <row r="28" spans="1:9" hidden="1">
-      <c r="A28" s="175"/>
+      <c r="A28" s="173"/>
       <c r="B28" s="138"/>
       <c r="C28" s="138"/>
       <c r="D28" s="138"/>
@@ -2583,16 +2582,16 @@
       <c r="H28" s="73"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="175" t="s">
+      <c r="A29" s="173" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="176"/>
+      <c r="B29" s="174"/>
       <c r="C29" s="138"/>
       <c r="D29" s="138"/>
       <c r="E29" s="138"/>
       <c r="F29" s="138"/>
       <c r="G29" s="138"/>
-      <c r="H29" s="243">
+      <c r="H29" s="73">
         <f>47767.67+1633.39+14700.53</f>
         <v>64101.59</v>
       </c>
@@ -2627,16 +2626,16 @@
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="192" t="s">
+      <c r="A32" s="215" t="s">
         <v>128</v>
       </c>
-      <c r="B32" s="192"/>
-      <c r="C32" s="192"/>
-      <c r="D32" s="192"/>
-      <c r="E32" s="192"/>
-      <c r="F32" s="192"/>
-      <c r="G32" s="192"/>
-      <c r="H32" s="192"/>
+      <c r="B32" s="215"/>
+      <c r="C32" s="215"/>
+      <c r="D32" s="215"/>
+      <c r="E32" s="215"/>
+      <c r="F32" s="215"/>
+      <c r="G32" s="215"/>
+      <c r="H32" s="215"/>
     </row>
     <row r="33" spans="1:10" ht="14.25" customHeight="1">
       <c r="A33" s="138" t="s">
@@ -2648,12 +2647,12 @@
       <c r="E33" s="138"/>
       <c r="F33" s="138"/>
       <c r="G33" s="138"/>
-      <c r="H33" s="243">
+      <c r="H33" s="73">
         <v>1490686.61</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="177" t="s">
+      <c r="A34" s="175" t="s">
         <v>98</v>
       </c>
       <c r="B34" s="138"/>
@@ -2662,7 +2661,7 @@
       <c r="E34" s="138"/>
       <c r="F34" s="138"/>
       <c r="G34" s="138"/>
-      <c r="H34" s="243">
+      <c r="H34" s="73">
         <v>30962.32</v>
       </c>
     </row>
@@ -2676,22 +2675,22 @@
       <c r="E35" s="138"/>
       <c r="F35" s="138"/>
       <c r="G35" s="138"/>
-      <c r="H35" s="178">
+      <c r="H35" s="176">
         <f>SUM(H33:H34)</f>
         <v>1521648.9300000002</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="206" t="s">
+      <c r="A36" s="225" t="s">
         <v>129</v>
       </c>
-      <c r="B36" s="206"/>
-      <c r="C36" s="206"/>
-      <c r="D36" s="206"/>
-      <c r="E36" s="206"/>
-      <c r="F36" s="206"/>
-      <c r="G36" s="206"/>
-      <c r="H36" s="206"/>
+      <c r="B36" s="225"/>
+      <c r="C36" s="225"/>
+      <c r="D36" s="225"/>
+      <c r="E36" s="225"/>
+      <c r="F36" s="225"/>
+      <c r="G36" s="225"/>
+      <c r="H36" s="225"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="80" t="s">
@@ -2703,13 +2702,13 @@
       <c r="E37" s="138"/>
       <c r="F37" s="138"/>
       <c r="G37" s="138"/>
-      <c r="H37" s="243">
+      <c r="H37" s="73">
         <v>85000</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="80" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B38" s="138"/>
       <c r="C38" s="138"/>
@@ -2718,14 +2717,13 @@
       <c r="F38" s="138"/>
       <c r="G38" s="138"/>
       <c r="H38" s="73">
-        <f>385625+924902.79</f>
-        <v>1310527.79</v>
-      </c>
-      <c r="I38" s="186"/>
+        <v>170591.71</v>
+      </c>
+      <c r="I38" s="184"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="80" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B39" s="138"/>
       <c r="C39" s="138"/>
@@ -2734,7 +2732,7 @@
       <c r="F39" s="138"/>
       <c r="G39" s="138"/>
       <c r="H39" s="73">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="I39" s="7"/>
     </row>
@@ -2748,13 +2746,13 @@
       <c r="E40" s="138"/>
       <c r="F40" s="138"/>
       <c r="G40" s="138"/>
-      <c r="H40" s="243">
+      <c r="H40" s="73">
         <v>23351.65</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="138" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B41" s="138"/>
       <c r="C41" s="138"/>
@@ -2762,13 +2760,13 @@
       <c r="E41" s="138"/>
       <c r="F41" s="138"/>
       <c r="G41" s="138"/>
-      <c r="H41" s="243">
+      <c r="H41" s="73">
         <v>65000</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="138" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B42" s="138"/>
       <c r="C42" s="138"/>
@@ -2776,13 +2774,13 @@
       <c r="E42" s="138"/>
       <c r="F42" s="138"/>
       <c r="G42" s="138"/>
-      <c r="H42" s="243">
+      <c r="H42" s="73">
         <v>47200</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="138" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B43" s="138"/>
       <c r="C43" s="138"/>
@@ -2790,13 +2788,13 @@
       <c r="E43" s="138"/>
       <c r="F43" s="138"/>
       <c r="G43" s="138"/>
-      <c r="H43" s="243">
+      <c r="H43" s="73">
         <v>50700</v>
       </c>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="244" t="s">
-        <v>161</v>
+      <c r="A44" s="80" t="s">
+        <v>159</v>
       </c>
       <c r="B44" s="138"/>
       <c r="C44" s="138"/>
@@ -2804,13 +2802,13 @@
       <c r="E44" s="138"/>
       <c r="F44" s="138"/>
       <c r="G44" s="138"/>
-      <c r="H44" s="243">
+      <c r="H44" s="73">
         <v>10000</v>
       </c>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="244" t="s">
-        <v>158</v>
+      <c r="A45" s="80" t="s">
+        <v>161</v>
       </c>
       <c r="B45" s="138"/>
       <c r="C45" s="138"/>
@@ -2818,8 +2816,8 @@
       <c r="E45" s="138"/>
       <c r="F45" s="138"/>
       <c r="G45" s="138"/>
-      <c r="H45" s="243">
-        <v>50000</v>
+      <c r="H45" s="73">
+        <v>250000</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2834,20 +2832,20 @@
       <c r="G46" s="138"/>
       <c r="H46" s="69">
         <f>SUM(H37:H45)</f>
-        <v>1841779.44</v>
+        <v>701843.36</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="206" t="s">
+      <c r="A47" s="225" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="206"/>
-      <c r="C47" s="206"/>
-      <c r="D47" s="206"/>
-      <c r="E47" s="206"/>
-      <c r="F47" s="206"/>
-      <c r="G47" s="206"/>
-      <c r="H47" s="206"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="138" t="s">
@@ -2876,7 +2874,7 @@
       <c r="E49" s="138"/>
       <c r="F49" s="138"/>
       <c r="G49" s="138"/>
-      <c r="H49" s="243">
+      <c r="H49" s="73">
         <v>45000</v>
       </c>
     </row>
@@ -2890,23 +2888,23 @@
       <c r="E50" s="138"/>
       <c r="F50" s="138"/>
       <c r="G50" s="138"/>
-      <c r="H50" s="178">
+      <c r="H50" s="176">
         <f>SUM(H48:H49)</f>
         <v>215100</v>
       </c>
       <c r="K50" s="7"/>
     </row>
     <row r="51" spans="1:11" s="6" customFormat="1">
-      <c r="A51" s="207" t="s">
+      <c r="A51" s="226" t="s">
         <v>131</v>
       </c>
-      <c r="B51" s="208"/>
-      <c r="C51" s="208"/>
-      <c r="D51" s="208"/>
-      <c r="E51" s="208"/>
-      <c r="F51" s="208"/>
-      <c r="G51" s="208"/>
-      <c r="H51" s="209"/>
+      <c r="B51" s="227"/>
+      <c r="C51" s="227"/>
+      <c r="D51" s="227"/>
+      <c r="E51" s="227"/>
+      <c r="F51" s="227"/>
+      <c r="G51" s="227"/>
+      <c r="H51" s="228"/>
     </row>
     <row r="52" spans="1:11" s="6" customFormat="1">
       <c r="A52" s="80" t="s">
@@ -2939,20 +2937,20 @@
       </c>
     </row>
     <row r="54" spans="1:11" s="6" customFormat="1">
-      <c r="A54" s="206" t="s">
+      <c r="A54" s="225" t="s">
         <v>132</v>
       </c>
-      <c r="B54" s="206"/>
-      <c r="C54" s="206"/>
-      <c r="D54" s="206"/>
-      <c r="E54" s="206"/>
-      <c r="F54" s="206"/>
-      <c r="G54" s="206"/>
-      <c r="H54" s="206"/>
+      <c r="B54" s="225"/>
+      <c r="C54" s="225"/>
+      <c r="D54" s="225"/>
+      <c r="E54" s="225"/>
+      <c r="F54" s="225"/>
+      <c r="G54" s="225"/>
+      <c r="H54" s="225"/>
     </row>
     <row r="55" spans="1:11" s="6" customFormat="1">
-      <c r="A55" s="244" t="s">
-        <v>159</v>
+      <c r="A55" s="80" t="s">
+        <v>158</v>
       </c>
       <c r="B55" s="80"/>
       <c r="C55" s="80"/>
@@ -2960,7 +2958,7 @@
       <c r="E55" s="80"/>
       <c r="F55" s="80"/>
       <c r="G55" s="80"/>
-      <c r="H55" s="243">
+      <c r="H55" s="73">
         <v>100000</v>
       </c>
     </row>
@@ -2975,14 +2973,14 @@
       <c r="H56" s="73"/>
     </row>
     <row r="57" spans="1:11" s="6" customFormat="1">
-      <c r="A57" s="174"/>
-      <c r="B57" s="174"/>
-      <c r="C57" s="174"/>
-      <c r="D57" s="174"/>
-      <c r="E57" s="174"/>
-      <c r="F57" s="174"/>
-      <c r="G57" s="174"/>
-      <c r="H57" s="173">
+      <c r="A57" s="80"/>
+      <c r="B57" s="80"/>
+      <c r="C57" s="80"/>
+      <c r="D57" s="80"/>
+      <c r="E57" s="80"/>
+      <c r="F57" s="80"/>
+      <c r="G57" s="80"/>
+      <c r="H57" s="69">
         <v>0</v>
       </c>
     </row>
@@ -3003,14 +3001,14 @@
       <c r="I58" s="60"/>
     </row>
     <row r="59" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A59" s="207"/>
-      <c r="B59" s="208"/>
-      <c r="C59" s="208"/>
-      <c r="D59" s="208"/>
-      <c r="E59" s="208"/>
-      <c r="F59" s="208"/>
-      <c r="G59" s="208"/>
-      <c r="H59" s="209"/>
+      <c r="A59" s="226"/>
+      <c r="B59" s="227"/>
+      <c r="C59" s="227"/>
+      <c r="D59" s="227"/>
+      <c r="E59" s="227"/>
+      <c r="F59" s="227"/>
+      <c r="G59" s="227"/>
+      <c r="H59" s="228"/>
     </row>
     <row r="60" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
       <c r="A60" s="81"/>
@@ -3050,60 +3048,60 @@
       </c>
     </row>
     <row r="63" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A63" s="213" t="s">
+      <c r="A63" s="207" t="s">
         <v>80</v>
       </c>
-      <c r="B63" s="214"/>
-      <c r="C63" s="214"/>
-      <c r="D63" s="214"/>
-      <c r="E63" s="214"/>
-      <c r="F63" s="214"/>
-      <c r="G63" s="214"/>
+      <c r="B63" s="208"/>
+      <c r="C63" s="208"/>
+      <c r="D63" s="208"/>
+      <c r="E63" s="208"/>
+      <c r="F63" s="208"/>
+      <c r="G63" s="208"/>
       <c r="H63" s="163">
         <f>H58</f>
         <v>100000</v>
       </c>
     </row>
     <row r="64" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A64" s="218"/>
-      <c r="B64" s="218"/>
-      <c r="C64" s="218"/>
-      <c r="D64" s="218"/>
-      <c r="E64" s="218"/>
-      <c r="F64" s="218"/>
-      <c r="G64" s="218"/>
-      <c r="H64" s="218"/>
+      <c r="A64" s="210"/>
+      <c r="B64" s="210"/>
+      <c r="C64" s="210"/>
+      <c r="D64" s="210"/>
+      <c r="E64" s="210"/>
+      <c r="F64" s="210"/>
+      <c r="G64" s="210"/>
+      <c r="H64" s="210"/>
     </row>
     <row r="65" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A65" s="219"/>
-      <c r="B65" s="219"/>
-      <c r="C65" s="219"/>
-      <c r="D65" s="219"/>
-      <c r="E65" s="219"/>
-      <c r="F65" s="219"/>
-      <c r="G65" s="219"/>
-      <c r="H65" s="219"/>
+      <c r="A65" s="211"/>
+      <c r="B65" s="211"/>
+      <c r="C65" s="211"/>
+      <c r="D65" s="211"/>
+      <c r="E65" s="211"/>
+      <c r="F65" s="211"/>
+      <c r="G65" s="211"/>
+      <c r="H65" s="211"/>
     </row>
     <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A66" s="217" t="s">
+      <c r="A66" s="209" t="s">
         <v>82</v>
       </c>
-      <c r="B66" s="217"/>
-      <c r="C66" s="217"/>
-      <c r="D66" s="217"/>
-      <c r="E66" s="217"/>
-      <c r="F66" s="217"/>
-      <c r="G66" s="217"/>
+      <c r="B66" s="209"/>
+      <c r="C66" s="209"/>
+      <c r="D66" s="209"/>
+      <c r="E66" s="209"/>
+      <c r="F66" s="209"/>
+      <c r="G66" s="209"/>
       <c r="H66" s="164"/>
     </row>
     <row r="67" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A67" s="198"/>
-      <c r="B67" s="199"/>
-      <c r="C67" s="199"/>
-      <c r="D67" s="199"/>
-      <c r="E67" s="199"/>
-      <c r="F67" s="199"/>
-      <c r="G67" s="200"/>
+      <c r="A67" s="218"/>
+      <c r="B67" s="219"/>
+      <c r="C67" s="219"/>
+      <c r="D67" s="219"/>
+      <c r="E67" s="219"/>
+      <c r="F67" s="219"/>
+      <c r="G67" s="220"/>
       <c r="H67" s="73"/>
     </row>
     <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
@@ -3132,91 +3130,91 @@
       <c r="H69" s="130"/>
     </row>
     <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A70" s="215" t="s">
+      <c r="A70" s="195" t="s">
         <v>81</v>
       </c>
-      <c r="B70" s="216"/>
-      <c r="C70" s="216"/>
-      <c r="D70" s="216"/>
-      <c r="E70" s="216"/>
-      <c r="F70" s="216"/>
-      <c r="G70" s="216"/>
+      <c r="B70" s="196"/>
+      <c r="C70" s="196"/>
+      <c r="D70" s="196"/>
+      <c r="E70" s="196"/>
+      <c r="F70" s="196"/>
+      <c r="G70" s="196"/>
       <c r="H70" s="131">
         <f>H68</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A71" s="193" t="s">
+      <c r="A71" s="204" t="s">
         <v>87</v>
       </c>
-      <c r="B71" s="194"/>
-      <c r="C71" s="194"/>
-      <c r="D71" s="194"/>
-      <c r="E71" s="194"/>
-      <c r="F71" s="194"/>
-      <c r="G71" s="195"/>
+      <c r="B71" s="205"/>
+      <c r="C71" s="205"/>
+      <c r="D71" s="205"/>
+      <c r="E71" s="205"/>
+      <c r="F71" s="205"/>
+      <c r="G71" s="206"/>
       <c r="H71" s="131"/>
     </row>
     <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A72" s="193" t="s">
+      <c r="A72" s="204" t="s">
         <v>92</v>
       </c>
-      <c r="B72" s="194"/>
-      <c r="C72" s="194"/>
-      <c r="D72" s="194"/>
-      <c r="E72" s="194"/>
-      <c r="F72" s="194"/>
-      <c r="G72" s="195"/>
+      <c r="B72" s="205"/>
+      <c r="C72" s="205"/>
+      <c r="D72" s="205"/>
+      <c r="E72" s="205"/>
+      <c r="F72" s="205"/>
+      <c r="G72" s="206"/>
       <c r="H72" s="131">
         <v>1000000</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="18">
-      <c r="A73" s="215" t="s">
+    <row r="73" spans="1:11" ht="18.75">
+      <c r="A73" s="195" t="s">
         <v>88</v>
       </c>
-      <c r="B73" s="216"/>
-      <c r="C73" s="216"/>
-      <c r="D73" s="216"/>
-      <c r="E73" s="216"/>
-      <c r="F73" s="216"/>
-      <c r="G73" s="216"/>
+      <c r="B73" s="196"/>
+      <c r="C73" s="196"/>
+      <c r="D73" s="196"/>
+      <c r="E73" s="196"/>
+      <c r="F73" s="196"/>
+      <c r="G73" s="196"/>
       <c r="H73" s="131">
         <f>H26+H35+H46+H50+H53+H31+H18+H22</f>
-        <v>3974846.96</v>
+        <v>2839589.88</v>
       </c>
       <c r="J73" s="172"/>
       <c r="K73" s="143"/>
     </row>
-    <row r="74" spans="1:11" ht="18">
-      <c r="A74" s="210" t="s">
+    <row r="74" spans="1:11" ht="18.75">
+      <c r="A74" s="201" t="s">
         <v>120</v>
       </c>
-      <c r="B74" s="211"/>
-      <c r="C74" s="211"/>
-      <c r="D74" s="211"/>
-      <c r="E74" s="211"/>
-      <c r="F74" s="211"/>
-      <c r="G74" s="212"/>
+      <c r="B74" s="202"/>
+      <c r="C74" s="202"/>
+      <c r="D74" s="202"/>
+      <c r="E74" s="202"/>
+      <c r="F74" s="202"/>
+      <c r="G74" s="203"/>
       <c r="H74" s="132">
         <f>H71+H73</f>
-        <v>3974846.96</v>
+        <v>2839589.88</v>
       </c>
       <c r="I74" s="127"/>
-      <c r="J74" s="220"/>
-      <c r="K74" s="220"/>
-    </row>
-    <row r="75" spans="1:11" ht="18">
-      <c r="A75" s="210" t="s">
+      <c r="J74" s="187"/>
+      <c r="K74" s="187"/>
+    </row>
+    <row r="75" spans="1:11" ht="18.75">
+      <c r="A75" s="201" t="s">
         <v>93</v>
       </c>
-      <c r="B75" s="211"/>
-      <c r="C75" s="211"/>
-      <c r="D75" s="211"/>
-      <c r="E75" s="211"/>
-      <c r="F75" s="211"/>
-      <c r="G75" s="212"/>
+      <c r="B75" s="202"/>
+      <c r="C75" s="202"/>
+      <c r="D75" s="202"/>
+      <c r="E75" s="202"/>
+      <c r="F75" s="202"/>
+      <c r="G75" s="203"/>
       <c r="H75" s="133">
         <f>H72+H70</f>
         <v>1000000</v>
@@ -3224,38 +3222,38 @@
       <c r="J75" s="143"/>
     </row>
     <row r="76" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A76" s="229" t="s">
+      <c r="A76" s="199" t="s">
         <v>83</v>
       </c>
-      <c r="B76" s="230"/>
-      <c r="C76" s="230"/>
-      <c r="D76" s="230"/>
-      <c r="E76" s="230"/>
-      <c r="F76" s="230"/>
-      <c r="G76" s="230"/>
+      <c r="B76" s="200"/>
+      <c r="C76" s="200"/>
+      <c r="D76" s="200"/>
+      <c r="E76" s="200"/>
+      <c r="F76" s="200"/>
+      <c r="G76" s="200"/>
       <c r="H76" s="134">
         <f>H73+H70</f>
-        <v>3974846.96</v>
+        <v>2839589.88</v>
       </c>
       <c r="J76" s="7"/>
     </row>
-    <row r="77" spans="1:11" ht="18" hidden="1">
-      <c r="A77" s="227" t="s">
+    <row r="77" spans="1:11" ht="18.75" hidden="1">
+      <c r="A77" s="197" t="s">
         <v>17</v>
       </c>
-      <c r="B77" s="228"/>
-      <c r="C77" s="228"/>
-      <c r="D77" s="228"/>
-      <c r="E77" s="228"/>
-      <c r="F77" s="228"/>
-      <c r="G77" s="228"/>
+      <c r="B77" s="198"/>
+      <c r="C77" s="198"/>
+      <c r="D77" s="198"/>
+      <c r="E77" s="198"/>
+      <c r="F77" s="198"/>
+      <c r="G77" s="198"/>
       <c r="H77" s="135">
         <f>H62</f>
         <v>0</v>
       </c>
       <c r="J77" s="7"/>
     </row>
-    <row r="78" spans="1:11" ht="18" hidden="1">
+    <row r="78" spans="1:11" ht="18.75" hidden="1">
       <c r="A78" s="136"/>
       <c r="B78" s="136"/>
       <c r="C78" s="136"/>
@@ -3266,7 +3264,7 @@
       <c r="H78" s="137"/>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" spans="1:11" ht="18" hidden="1">
+    <row r="79" spans="1:11" ht="18.75" hidden="1">
       <c r="A79" s="136"/>
       <c r="B79" s="136"/>
       <c r="C79" s="136"/>
@@ -3277,7 +3275,7 @@
       <c r="H79" s="137"/>
       <c r="J79" s="7"/>
     </row>
-    <row r="80" spans="1:11" ht="18" hidden="1">
+    <row r="80" spans="1:11" ht="18.75" hidden="1">
       <c r="A80" s="136"/>
       <c r="B80" s="136"/>
       <c r="C80" s="136"/>
@@ -3298,19 +3296,19 @@
       <c r="G81" s="138"/>
       <c r="H81" s="138"/>
     </row>
-    <row r="82" spans="1:11" ht="18">
-      <c r="A82" s="224" t="s">
+    <row r="82" spans="1:11" ht="18.75">
+      <c r="A82" s="192" t="s">
         <v>10</v>
       </c>
-      <c r="B82" s="225"/>
-      <c r="C82" s="225"/>
-      <c r="D82" s="225"/>
-      <c r="E82" s="225"/>
-      <c r="F82" s="225"/>
-      <c r="G82" s="225"/>
-      <c r="H82" s="226"/>
-    </row>
-    <row r="83" spans="1:11" ht="18">
+      <c r="B82" s="193"/>
+      <c r="C82" s="193"/>
+      <c r="D82" s="193"/>
+      <c r="E82" s="193"/>
+      <c r="F82" s="193"/>
+      <c r="G82" s="193"/>
+      <c r="H82" s="194"/>
+    </row>
+    <row r="83" spans="1:11" ht="18.75">
       <c r="A83" s="139" t="s">
         <v>12</v>
       </c>
@@ -3321,12 +3319,12 @@
       <c r="F83" s="140"/>
       <c r="G83" s="140"/>
       <c r="H83" s="141">
-        <v>3532612.5527224625</v>
+        <v>3564156.5524669625</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="81" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B84" s="82"/>
       <c r="C84" s="82"/>
@@ -3336,12 +3334,12 @@
       <c r="G84" s="82"/>
       <c r="H84" s="142">
         <f>Planilla!G32</f>
-        <v>3936249.2638619998</v>
+        <v>4001448.7106899992</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="78" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B85" s="79"/>
       <c r="C85" s="79"/>
@@ -3349,9 +3347,9 @@
       <c r="E85" s="79"/>
       <c r="F85" s="79"/>
       <c r="G85" s="79"/>
-      <c r="H85" s="182">
+      <c r="H85" s="180">
         <f>-(H76)</f>
-        <v>-3974846.96</v>
+        <v>-2839589.88</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -3364,7 +3362,7 @@
       <c r="E86" s="79"/>
       <c r="F86" s="79"/>
       <c r="G86" s="79"/>
-      <c r="H86" s="182">
+      <c r="H86" s="180">
         <f>-H63</f>
         <v>-100000</v>
       </c>
@@ -3372,7 +3370,7 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="78" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B87" s="79"/>
       <c r="C87" s="79"/>
@@ -3411,7 +3409,7 @@
       <c r="G89" s="4"/>
       <c r="H89" s="98"/>
     </row>
-    <row r="90" spans="1:11" ht="18">
+    <row r="90" spans="1:11" ht="18.75">
       <c r="A90" s="22" t="s">
         <v>11</v>
       </c>
@@ -3423,23 +3421,23 @@
       <c r="G90" s="23"/>
       <c r="H90" s="84">
         <f>SUM(H83:H89)</f>
-        <v>3581257.1324669626</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="15" thickBot="1"/>
-    <row r="92" spans="1:11" ht="16.2" thickBot="1">
-      <c r="A92" s="221" t="s">
+        <v>4813257.659039462</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="92" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A92" s="189" t="s">
         <v>97</v>
       </c>
-      <c r="B92" s="222"/>
-      <c r="C92" s="222"/>
-      <c r="D92" s="222"/>
-      <c r="E92" s="222"/>
-      <c r="F92" s="222"/>
-      <c r="G92" s="222"/>
-      <c r="H92" s="223"/>
-    </row>
-    <row r="93" spans="1:11" ht="15.6">
+      <c r="B92" s="190"/>
+      <c r="C92" s="190"/>
+      <c r="D92" s="190"/>
+      <c r="E92" s="190"/>
+      <c r="F92" s="190"/>
+      <c r="G92" s="190"/>
+      <c r="H92" s="191"/>
+    </row>
+    <row r="93" spans="1:11" ht="15.75">
       <c r="A93" s="87" t="s">
         <v>12</v>
       </c>
@@ -3501,61 +3499,47 @@
       </c>
     </row>
     <row r="100" spans="1:8" hidden="1">
-      <c r="A100" s="202"/>
-      <c r="B100" s="202"/>
-      <c r="C100" s="202"/>
-      <c r="D100" s="202"/>
-      <c r="E100" s="202"/>
-      <c r="F100" s="202"/>
-      <c r="G100" s="202"/>
-      <c r="H100" s="202"/>
+      <c r="A100" s="188"/>
+      <c r="B100" s="188"/>
+      <c r="C100" s="188"/>
+      <c r="D100" s="188"/>
+      <c r="E100" s="188"/>
+      <c r="F100" s="188"/>
+      <c r="G100" s="188"/>
+      <c r="H100" s="188"/>
     </row>
     <row r="101" spans="1:8" hidden="1">
-      <c r="A101" s="202"/>
-      <c r="B101" s="202"/>
-      <c r="C101" s="202"/>
-      <c r="D101" s="202"/>
-      <c r="E101" s="202"/>
-      <c r="F101" s="202"/>
-      <c r="G101" s="202"/>
-      <c r="H101" s="202"/>
+      <c r="A101" s="188"/>
+      <c r="B101" s="188"/>
+      <c r="C101" s="188"/>
+      <c r="D101" s="188"/>
+      <c r="E101" s="188"/>
+      <c r="F101" s="188"/>
+      <c r="G101" s="188"/>
+      <c r="H101" s="188"/>
     </row>
     <row r="102" spans="1:8" hidden="1">
-      <c r="A102" s="202"/>
-      <c r="B102" s="202"/>
-      <c r="C102" s="202"/>
-      <c r="D102" s="202"/>
-      <c r="E102" s="202"/>
-      <c r="F102" s="202"/>
-      <c r="G102" s="202"/>
-      <c r="H102" s="202"/>
+      <c r="A102" s="188"/>
+      <c r="B102" s="188"/>
+      <c r="C102" s="188"/>
+      <c r="D102" s="188"/>
+      <c r="E102" s="188"/>
+      <c r="F102" s="188"/>
+      <c r="G102" s="188"/>
+      <c r="H102" s="188"/>
     </row>
     <row r="103" spans="1:8" hidden="1">
-      <c r="A103" s="202"/>
-      <c r="B103" s="202"/>
-      <c r="C103" s="202"/>
-      <c r="D103" s="202"/>
-      <c r="E103" s="202"/>
-      <c r="F103" s="202"/>
-      <c r="G103" s="202"/>
-      <c r="H103" s="202"/>
+      <c r="A103" s="188"/>
+      <c r="B103" s="188"/>
+      <c r="C103" s="188"/>
+      <c r="D103" s="188"/>
+      <c r="E103" s="188"/>
+      <c r="F103" s="188"/>
+      <c r="G103" s="188"/>
+      <c r="H103" s="188"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="A100:H103"/>
-    <mergeCell ref="A92:H92"/>
-    <mergeCell ref="A82:H82"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A63:G63"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A64:H65"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A72:G72"/>
@@ -3571,6 +3555,20 @@
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A47:H47"/>
     <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A64:H65"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="A100:H103"/>
+    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A82:H82"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A75:G75"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3581,24 +3579,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.21875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" customWidth="1"/>
-    <col min="14" max="14" width="13.44140625" customWidth="1"/>
-    <col min="15" max="15" width="15.109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="26.25" customHeight="1">
@@ -3630,7 +3628,7 @@
       <c r="A2" s="61"/>
       <c r="B2" s="61"/>
       <c r="C2" s="125">
-        <v>1310527.79</v>
+        <v>170591.71</v>
       </c>
       <c r="D2" s="61"/>
       <c r="E2" s="61"/>
@@ -3691,16 +3689,16 @@
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="120"/>
-      <c r="B5" s="232">
+      <c r="B5" s="230">
         <f>C3-B7</f>
-        <v>2771419.75</v>
-      </c>
-      <c r="C5" s="232"/>
+        <v>3911355.83</v>
+      </c>
+      <c r="C5" s="230"/>
       <c r="D5" s="21"/>
-      <c r="E5" s="238">
+      <c r="E5" s="236">
         <v>70000</v>
       </c>
-      <c r="F5" s="239"/>
+      <c r="F5" s="237"/>
       <c r="G5" s="114"/>
       <c r="H5" s="114"/>
       <c r="I5" s="114"/>
@@ -3713,15 +3711,15 @@
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="120"/>
-      <c r="B6" s="234" t="s">
+      <c r="B6" s="232" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="235"/>
+      <c r="C6" s="233"/>
       <c r="D6" s="21"/>
-      <c r="E6" s="234" t="s">
-        <v>153</v>
-      </c>
-      <c r="F6" s="235"/>
+      <c r="E6" s="232" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" s="233"/>
       <c r="G6" s="114"/>
       <c r="H6" s="114"/>
       <c r="I6" s="114"/>
@@ -3734,16 +3732,16 @@
     </row>
     <row r="7" spans="1:17" ht="18.75" customHeight="1">
       <c r="A7" s="120"/>
-      <c r="B7" s="232">
+      <c r="B7" s="230">
         <f>C2</f>
-        <v>1310527.79</v>
-      </c>
-      <c r="C7" s="232"/>
+        <v>170591.71</v>
+      </c>
+      <c r="C7" s="230"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="236">
+      <c r="E7" s="234">
         <v>1000000</v>
       </c>
-      <c r="F7" s="237"/>
+      <c r="F7" s="235"/>
       <c r="G7" s="114"/>
       <c r="H7" s="114"/>
       <c r="I7" s="114"/>
@@ -3818,11 +3816,11 @@
         <v>4.0500000000000001E-2</v>
       </c>
       <c r="F9" s="98">
-        <v>193689.46354500001</v>
-      </c>
-      <c r="G9" s="179">
+        <v>205818.87537000002</v>
+      </c>
+      <c r="G9" s="177">
         <f>F9</f>
-        <v>193689.46354500001</v>
+        <v>205818.87537000002</v>
       </c>
       <c r="H9" s="68">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
@@ -3846,15 +3844,15 @@
       </c>
       <c r="M9" s="169">
         <f>B$5*E9</f>
-        <v>112242.49987500001</v>
+        <v>158409.911115</v>
       </c>
       <c r="N9" s="169">
         <f>B$7*E9</f>
-        <v>53076.375495</v>
-      </c>
-      <c r="O9" s="187">
+        <v>6908.9642549999999</v>
+      </c>
+      <c r="O9" s="185">
         <f>H9+I9-J9+K9+M9+N9+L9</f>
-        <v>205818.87537000002</v>
+        <v>205818.87536999999</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1">
@@ -3872,11 +3870,11 @@
         <v>6.4799999999999996E-2</v>
       </c>
       <c r="F10" s="17">
-        <v>309903.14167199994</v>
-      </c>
-      <c r="G10" s="179">
+        <v>329310.20059199998</v>
+      </c>
+      <c r="G10" s="177">
         <f>F10</f>
-        <v>309903.14167199994</v>
+        <v>329310.20059199998</v>
       </c>
       <c r="H10" s="24">
         <f t="shared" ref="H10:H31" si="0">IF(F10&gt;G10,F10-G10,0)</f>
@@ -3900,13 +3898,13 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" ref="M10:M31" si="4">B$5*E10</f>
-        <v>179587.99979999999</v>
+        <v>253455.85778399999</v>
       </c>
       <c r="N10" s="25">
         <f t="shared" ref="N10:N31" si="5">B$7*E10</f>
-        <v>84922.200792000003</v>
-      </c>
-      <c r="O10" s="187">
+        <v>11054.342807999999</v>
+      </c>
+      <c r="O10" s="185">
         <f t="shared" ref="O10:O31" si="6">H10+I10-J10+K10+M10+N10+L10</f>
         <v>329310.20059199998</v>
       </c>
@@ -3928,11 +3926,11 @@
         <v>4.82E-2</v>
       </c>
       <c r="F11" s="98">
-        <v>230514.37389799999</v>
-      </c>
-      <c r="G11" s="179">
+        <v>244949.87142799998</v>
+      </c>
+      <c r="G11" s="177">
         <f>F11</f>
-        <v>230514.37389799999</v>
+        <v>244949.87142799998</v>
       </c>
       <c r="H11" s="68">
         <f t="shared" si="0"/>
@@ -3956,15 +3954,15 @@
       </c>
       <c r="M11" s="169">
         <f t="shared" si="4"/>
-        <v>133582.43195</v>
+        <v>188527.35100600001</v>
       </c>
       <c r="N11" s="169">
         <f t="shared" si="5"/>
-        <v>63167.439478</v>
-      </c>
-      <c r="O11" s="187">
+        <v>8222.5204219999996</v>
+      </c>
+      <c r="O11" s="185">
         <f t="shared" si="6"/>
-        <v>244949.87142799998</v>
+        <v>244949.87142800001</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15" customHeight="1">
@@ -3984,16 +3982,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F12" s="148">
-        <v>3699231.9955503126</v>
-      </c>
-      <c r="G12" s="180"/>
+        <v>4107987.7727756742</v>
+      </c>
+      <c r="G12" s="178"/>
       <c r="H12" s="149">
         <f t="shared" si="0"/>
-        <v>3699231.9955503126</v>
+        <v>4107987.7727756742</v>
       </c>
       <c r="I12" s="149">
         <f t="shared" si="7"/>
-        <v>136871.58383536158</v>
+        <v>151995.54759269996</v>
       </c>
       <c r="J12" s="149">
         <f t="shared" si="1"/>
@@ -4009,15 +4007,15 @@
       </c>
       <c r="M12" s="150">
         <f t="shared" si="4"/>
-        <v>148270.95662499999</v>
+        <v>209257.53690499999</v>
       </c>
       <c r="N12" s="150">
         <f t="shared" si="5"/>
-        <v>70113.236764999994</v>
-      </c>
-      <c r="O12" s="188">
+        <v>9126.6564849999995</v>
+      </c>
+      <c r="O12" s="186">
         <f t="shared" si="6"/>
-        <v>4107987.7727756742</v>
+        <v>4531867.5137583734</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1">
@@ -4035,11 +4033,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F13" s="17">
-        <v>184124.55176499998</v>
-      </c>
-      <c r="G13" s="179">
+        <v>195654.98028999998</v>
+      </c>
+      <c r="G13" s="177">
         <f>F13</f>
-        <v>184124.55176499998</v>
+        <v>195654.98028999998</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" si="0"/>
@@ -4063,15 +4061,15 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="4"/>
-        <v>106699.66037499999</v>
+        <v>150587.19945499999</v>
       </c>
       <c r="N13" s="25">
         <f t="shared" si="5"/>
-        <v>50455.319915</v>
-      </c>
-      <c r="O13" s="187">
+        <v>6567.7808349999996</v>
+      </c>
+      <c r="O13" s="185">
         <f t="shared" si="6"/>
-        <v>195654.98028999998</v>
+        <v>195654.98029000001</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1">
@@ -4091,11 +4089,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F14" s="17">
-        <v>171690.166451</v>
-      </c>
-      <c r="G14" s="179">
+        <v>182441.91668600001</v>
+      </c>
+      <c r="G14" s="177">
         <f>F14</f>
-        <v>171690.166451</v>
+        <v>182441.91668600001</v>
       </c>
       <c r="H14" s="24">
         <f t="shared" si="0"/>
@@ -4119,13 +4117,13 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="4"/>
-        <v>99493.969024999999</v>
+        <v>140417.67429700002</v>
       </c>
       <c r="N14" s="25">
         <f t="shared" si="5"/>
-        <v>47047.947661000006</v>
-      </c>
-      <c r="O14" s="187">
+        <v>6124.242389</v>
+      </c>
+      <c r="O14" s="185">
         <f t="shared" si="6"/>
         <v>182441.91668600001</v>
       </c>
@@ -4147,11 +4145,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F15" s="17">
-        <v>115193.67384599999</v>
-      </c>
-      <c r="G15" s="179">
+        <v>156136.77765</v>
+      </c>
+      <c r="G15" s="177">
         <f>F15</f>
-        <v>115193.67384599999</v>
+        <v>156136.77765</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="0"/>
@@ -4175,16 +4173,16 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="4"/>
-        <v>114736.77765</v>
+        <v>161930.13136200001</v>
       </c>
       <c r="N15" s="25">
         <v>0</v>
       </c>
-      <c r="O15" s="187">
+      <c r="O15" s="185">
         <f t="shared" si="6"/>
-        <v>156136.77765</v>
-      </c>
-      <c r="Q15" s="183"/>
+        <v>203330.13136200001</v>
+      </c>
+      <c r="Q15" s="181"/>
     </row>
     <row r="16" spans="1:17" ht="15" customHeight="1">
       <c r="A16" s="51">
@@ -4203,11 +4201,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F16" s="17">
-        <v>255861.39011499999</v>
-      </c>
-      <c r="G16" s="179">
+        <v>271884.19338999997</v>
+      </c>
+      <c r="G16" s="177">
         <f>F16</f>
-        <v>255861.39011499999</v>
+        <v>271884.19338999997</v>
       </c>
       <c r="H16" s="24">
         <f t="shared" si="0"/>
@@ -4231,17 +4229,17 @@
       </c>
       <c r="M16" s="25">
         <f t="shared" si="4"/>
-        <v>148270.95662499999</v>
+        <v>209257.53690499999</v>
       </c>
       <c r="N16" s="25">
         <f t="shared" si="5"/>
-        <v>70113.236764999994</v>
-      </c>
-      <c r="O16" s="187">
+        <v>9126.6564849999995</v>
+      </c>
+      <c r="O16" s="185">
         <f t="shared" si="6"/>
         <v>271884.19338999997</v>
       </c>
-      <c r="Q16" s="183"/>
+      <c r="Q16" s="181"/>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1">
       <c r="A17" s="51">
@@ -4260,19 +4258,16 @@
         <v>3.85E-2</v>
       </c>
       <c r="F17" s="17">
-        <v>184124.55176499998</v>
-      </c>
-      <c r="G17" s="179">
-        <f>F17</f>
-        <v>184124.55176499998</v>
-      </c>
+        <v>195654.98028999998</v>
+      </c>
+      <c r="G17" s="177"/>
       <c r="H17" s="24">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>195654.98028999998</v>
       </c>
       <c r="I17" s="24">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7239.2342707300004</v>
       </c>
       <c r="J17" s="24">
         <f t="shared" si="1"/>
@@ -4288,17 +4283,17 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="4"/>
-        <v>106699.66037499999</v>
+        <v>150587.19945499999</v>
       </c>
       <c r="N17" s="25">
         <f t="shared" si="5"/>
-        <v>50455.319915</v>
-      </c>
-      <c r="O17" s="187">
+        <v>6567.7808349999996</v>
+      </c>
+      <c r="O17" s="185">
         <f t="shared" si="6"/>
-        <v>195654.98028999998</v>
-      </c>
-      <c r="Q17" s="183"/>
+        <v>398549.19485072995</v>
+      </c>
+      <c r="Q17" s="181"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1">
       <c r="A18" s="165">
@@ -4315,19 +4310,19 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F18" s="98">
-        <v>318869.51383709081</v>
-      </c>
-      <c r="G18" s="179">
-        <f>RESUMEN!H49+RESUMEN!H37+RESUMEN!H41</f>
+        <v>321264.60253506317</v>
+      </c>
+      <c r="G18" s="177">
+        <f>RESUMEN!H49+RESUMEN!H41+RESUMEN!H37</f>
         <v>195000</v>
       </c>
       <c r="H18" s="68">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
-        <v>123869.51383709081</v>
+        <v>126264.60253506317</v>
       </c>
       <c r="I18" s="68">
         <f t="shared" si="7"/>
-        <v>4583.1720119723605</v>
+        <v>4671.7902937973377</v>
       </c>
       <c r="J18" s="68">
         <f t="shared" si="1"/>
@@ -4343,17 +4338,17 @@
       </c>
       <c r="M18" s="169">
         <f t="shared" si="4"/>
-        <v>99493.969024999999</v>
+        <v>140417.67429700002</v>
       </c>
       <c r="N18" s="169">
         <f t="shared" si="5"/>
-        <v>47047.947661000006</v>
-      </c>
-      <c r="O18" s="187">
+        <v>6124.242389</v>
+      </c>
+      <c r="O18" s="185">
         <f t="shared" si="6"/>
-        <v>310894.60253506317</v>
-      </c>
-      <c r="Q18" s="183"/>
+        <v>313378.30951486056</v>
+      </c>
+      <c r="Q18" s="181"/>
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1">
       <c r="A19" s="144">
@@ -4372,16 +4367,16 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F19" s="148">
-        <v>2560026.5391890835</v>
-      </c>
-      <c r="G19" s="180"/>
+        <v>2865140.14929508</v>
+      </c>
+      <c r="G19" s="178"/>
       <c r="H19" s="149">
         <f t="shared" si="0"/>
-        <v>2560026.5391890835</v>
+        <v>2865140.14929508</v>
       </c>
       <c r="I19" s="149">
         <f t="shared" si="7"/>
-        <v>94720.981949996101</v>
+        <v>106010.18552391797</v>
       </c>
       <c r="J19" s="149">
         <f t="shared" si="1"/>
@@ -4397,17 +4392,17 @@
       </c>
       <c r="M19" s="150">
         <f t="shared" si="4"/>
-        <v>114736.77765</v>
+        <v>161930.13136200001</v>
       </c>
       <c r="N19" s="150">
         <f t="shared" si="5"/>
-        <v>54255.850506000002</v>
-      </c>
-      <c r="O19" s="188">
+        <v>7062.4967939999997</v>
+      </c>
+      <c r="O19" s="186">
         <f t="shared" si="6"/>
-        <v>2865140.14929508</v>
-      </c>
-      <c r="Q19" s="183"/>
+        <v>3181542.9629749977</v>
+      </c>
+      <c r="Q19" s="181"/>
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1">
       <c r="A20" s="51">
@@ -4426,11 +4421,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F20" s="17">
-        <v>255861.39011499999</v>
-      </c>
-      <c r="G20" s="179">
+        <v>271884.19338999997</v>
+      </c>
+      <c r="G20" s="177">
         <f>F20</f>
-        <v>255861.39011499999</v>
+        <v>271884.19338999997</v>
       </c>
       <c r="H20" s="24">
         <f t="shared" si="0"/>
@@ -4454,17 +4449,17 @@
       </c>
       <c r="M20" s="25">
         <f t="shared" si="4"/>
-        <v>148270.95662499999</v>
+        <v>209257.53690499999</v>
       </c>
       <c r="N20" s="25">
         <f t="shared" si="5"/>
-        <v>70113.236764999994</v>
-      </c>
-      <c r="O20" s="187">
+        <v>9126.6564849999995</v>
+      </c>
+      <c r="O20" s="185">
         <f t="shared" si="6"/>
         <v>271884.19338999997</v>
       </c>
-      <c r="Q20" s="183"/>
+      <c r="Q20" s="181"/>
     </row>
     <row r="21" spans="1:18" ht="15" customHeight="1">
       <c r="A21" s="144">
@@ -4483,18 +4478,18 @@
         <v>3.85E-2</v>
       </c>
       <c r="F21" s="148">
-        <v>1162315.7981436667</v>
-      </c>
-      <c r="G21" s="181">
-        <v>107124.55</v>
+        <v>1289888.3046149821</v>
+      </c>
+      <c r="G21" s="179">
+        <v>106699.66</v>
       </c>
       <c r="H21" s="149">
         <f t="shared" si="0"/>
-        <v>1055191.2481436667</v>
+        <v>1183188.6446149822</v>
       </c>
       <c r="I21" s="149">
         <f t="shared" si="7"/>
-        <v>39042.076181315671</v>
+        <v>43777.979850754346</v>
       </c>
       <c r="J21" s="149">
         <f t="shared" si="1"/>
@@ -4510,17 +4505,17 @@
       </c>
       <c r="M21" s="150">
         <f t="shared" si="4"/>
-        <v>106699.66037499999</v>
+        <v>150587.19945499999</v>
       </c>
       <c r="N21" s="150">
         <f t="shared" si="5"/>
-        <v>50455.319915</v>
-      </c>
-      <c r="O21" s="188">
+        <v>6567.7808349999996</v>
+      </c>
+      <c r="O21" s="186">
         <f t="shared" si="6"/>
-        <v>1289888.3046149821</v>
-      </c>
-      <c r="Q21" s="183"/>
+        <v>1422621.6047557367</v>
+      </c>
+      <c r="Q21" s="181"/>
     </row>
     <row r="22" spans="1:18" ht="15" customHeight="1">
       <c r="A22" s="51">
@@ -4539,11 +4534,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F22" s="17">
-        <v>171690.166451</v>
-      </c>
-      <c r="G22" s="179">
+        <v>182441.91668600001</v>
+      </c>
+      <c r="G22" s="177">
         <f>F22</f>
-        <v>171690.166451</v>
+        <v>182441.91668600001</v>
       </c>
       <c r="H22" s="24">
         <f t="shared" si="0"/>
@@ -4567,17 +4562,17 @@
       </c>
       <c r="M22" s="25">
         <f t="shared" si="4"/>
-        <v>99493.969024999999</v>
+        <v>140417.67429700002</v>
       </c>
       <c r="N22" s="25">
         <f t="shared" si="5"/>
-        <v>47047.947661000006</v>
-      </c>
-      <c r="O22" s="187">
+        <v>6124.242389</v>
+      </c>
+      <c r="O22" s="185">
         <f t="shared" si="6"/>
         <v>182441.91668600001</v>
       </c>
-      <c r="Q22" s="183"/>
+      <c r="Q22" s="181"/>
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1">
       <c r="A23" s="51">
@@ -4596,11 +4591,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F23" s="17">
-        <v>197993.67384599999</v>
-      </c>
-      <c r="G23" s="179">
-        <f>F23</f>
-        <v>197993.67384599999</v>
+        <v>210392.62815599999</v>
+      </c>
+      <c r="G23" s="177">
+        <f>114736+95655.86+1</f>
+        <v>210392.86</v>
       </c>
       <c r="H23" s="24">
         <f t="shared" si="0"/>
@@ -4612,7 +4607,7 @@
       </c>
       <c r="J23" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.23184399999445304</v>
       </c>
       <c r="K23" s="24">
         <f t="shared" si="2"/>
@@ -4624,17 +4619,17 @@
       </c>
       <c r="M23" s="25">
         <f t="shared" si="4"/>
-        <v>114736.77765</v>
+        <v>161930.13136200001</v>
       </c>
       <c r="N23" s="25">
         <f t="shared" si="5"/>
-        <v>54255.850506000002</v>
-      </c>
-      <c r="O23" s="187">
+        <v>7062.4967939999997</v>
+      </c>
+      <c r="O23" s="185">
         <f t="shared" si="6"/>
-        <v>210392.62815599999</v>
-      </c>
-      <c r="Q23" s="183"/>
+        <v>210392.39631200003</v>
+      </c>
+      <c r="Q23" s="181"/>
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1">
       <c r="A24" s="51">
@@ -4651,11 +4646,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F24" s="17">
-        <v>255861.39011499999</v>
-      </c>
-      <c r="G24" s="179">
+        <v>271884.19338999997</v>
+      </c>
+      <c r="G24" s="177">
         <f>F24</f>
-        <v>255861.39011499999</v>
+        <v>271884.19338999997</v>
       </c>
       <c r="H24" s="24">
         <f t="shared" si="0"/>
@@ -4679,17 +4674,17 @@
       </c>
       <c r="M24" s="25">
         <f t="shared" si="4"/>
-        <v>148270.95662499999</v>
+        <v>209257.53690499999</v>
       </c>
       <c r="N24" s="25">
         <f t="shared" si="5"/>
-        <v>70113.236764999994</v>
-      </c>
-      <c r="O24" s="187">
+        <v>9126.6564849999995</v>
+      </c>
+      <c r="O24" s="185">
         <f t="shared" si="6"/>
         <v>271884.19338999997</v>
       </c>
-      <c r="Q24" s="183"/>
+      <c r="Q24" s="181"/>
     </row>
     <row r="25" spans="1:18" s="1" customFormat="1" ht="15.75" customHeight="1">
       <c r="A25" s="51">
@@ -4708,11 +4703,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F25" s="17">
-        <v>184124.55176499998</v>
-      </c>
-      <c r="G25" s="179">
-        <f>F25</f>
-        <v>184124.55176499998</v>
+        <v>195654.98028999998</v>
+      </c>
+      <c r="G25" s="177">
+        <f>106699+88955+1</f>
+        <v>195655</v>
       </c>
       <c r="H25" s="24">
         <f t="shared" si="0"/>
@@ -4724,7 +4719,7 @@
       </c>
       <c r="J25" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.9710000022314489E-2</v>
       </c>
       <c r="K25" s="24">
         <f t="shared" si="2"/>
@@ -4736,17 +4731,17 @@
       </c>
       <c r="M25" s="25">
         <f t="shared" si="4"/>
-        <v>106699.66037499999</v>
+        <v>150587.19945499999</v>
       </c>
       <c r="N25" s="25">
         <f t="shared" si="5"/>
-        <v>50455.319915</v>
-      </c>
-      <c r="O25" s="187">
+        <v>6567.7808349999996</v>
+      </c>
+      <c r="O25" s="185">
         <f t="shared" si="6"/>
-        <v>195654.98028999998</v>
-      </c>
-      <c r="Q25" s="184"/>
+        <v>195654.96057999998</v>
+      </c>
+      <c r="Q25" s="182"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1">
       <c r="A26" s="51">
@@ -4763,11 +4758,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F26" s="17">
-        <v>171690.166451</v>
-      </c>
-      <c r="G26" s="179">
+        <v>182441.91668600001</v>
+      </c>
+      <c r="G26" s="177">
         <f>F26</f>
-        <v>171690.166451</v>
+        <v>182441.91668600001</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="0"/>
@@ -4791,17 +4786,17 @@
       </c>
       <c r="M26" s="25">
         <f t="shared" si="4"/>
-        <v>99493.969024999999</v>
+        <v>140417.67429700002</v>
       </c>
       <c r="N26" s="25">
         <f t="shared" si="5"/>
-        <v>47047.947661000006</v>
-      </c>
-      <c r="O26" s="187">
+        <v>6124.242389</v>
+      </c>
+      <c r="O26" s="185">
         <f t="shared" si="6"/>
         <v>182441.91668600001</v>
       </c>
-      <c r="Q26" s="183"/>
+      <c r="Q26" s="181"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1">
       <c r="A27" s="144">
@@ -4820,18 +4815,18 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F27" s="148">
-        <v>3046839.1915586414</v>
-      </c>
-      <c r="G27" s="180">
-        <v>197993.67</v>
+        <v>3164645.4340123115</v>
+      </c>
+      <c r="G27" s="178">
+        <v>210362.63</v>
       </c>
       <c r="H27" s="171">
         <f t="shared" si="0"/>
-        <v>2848845.5215586415</v>
+        <v>2954282.8040123116</v>
       </c>
       <c r="I27" s="149">
         <f t="shared" si="7"/>
-        <v>105407.28429766974</v>
+        <v>109308.46374845554</v>
       </c>
       <c r="J27" s="149">
         <f t="shared" si="1"/>
@@ -4847,19 +4842,19 @@
       </c>
       <c r="M27" s="150">
         <f t="shared" si="4"/>
-        <v>114736.77765</v>
+        <v>161930.13136200001</v>
       </c>
       <c r="N27" s="150">
         <f t="shared" si="5"/>
-        <v>54255.850506000002</v>
-      </c>
-      <c r="O27" s="188">
+        <v>7062.4967939999997</v>
+      </c>
+      <c r="O27" s="186">
         <f t="shared" si="6"/>
-        <v>3164645.4340123115</v>
-      </c>
-      <c r="P27" s="185">
+        <v>3273983.895916767</v>
+      </c>
+      <c r="P27" s="183">
         <f>M27+N27</f>
-        <v>168992.62815599999</v>
+        <v>168992.62815600002</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="17.25" customHeight="1">
@@ -4877,16 +4872,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F28" s="17">
-        <v>1659893.3319441385</v>
-      </c>
-      <c r="G28" s="179"/>
+        <v>1993193.5786160715</v>
+      </c>
+      <c r="G28" s="177"/>
       <c r="H28" s="68">
         <f t="shared" si="0"/>
-        <v>1659893.3319441385</v>
+        <v>1993193.5786160715</v>
       </c>
       <c r="I28" s="24">
         <f t="shared" si="7"/>
-        <v>61416.053281933135</v>
+        <v>73748.162408794655</v>
       </c>
       <c r="J28" s="24">
         <f t="shared" si="1"/>
@@ -4899,15 +4894,15 @@
       </c>
       <c r="M28" s="25">
         <f t="shared" si="4"/>
-        <v>148270.95662499999</v>
+        <v>209257.53690499999</v>
       </c>
       <c r="N28" s="25">
         <f t="shared" si="5"/>
-        <v>70113.236764999994</v>
-      </c>
-      <c r="O28" s="187">
+        <v>9126.6564849999995</v>
+      </c>
+      <c r="O28" s="185">
         <f t="shared" si="6"/>
-        <v>1993193.5786160715</v>
+        <v>2338825.9344148664</v>
       </c>
       <c r="P28" s="7"/>
     </row>
@@ -4926,11 +4921,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F29" s="17">
-        <v>184124.55176499998</v>
-      </c>
-      <c r="G29" s="179">
+        <v>195654.98028999998</v>
+      </c>
+      <c r="G29" s="177">
         <f>F29</f>
-        <v>184124.55176499998</v>
+        <v>195654.98028999998</v>
       </c>
       <c r="H29" s="24">
         <f t="shared" si="0"/>
@@ -4954,15 +4949,15 @@
       </c>
       <c r="M29" s="25">
         <f t="shared" si="4"/>
-        <v>106699.66037499999</v>
+        <v>150587.19945499999</v>
       </c>
       <c r="N29" s="25">
         <f t="shared" si="5"/>
-        <v>50455.319915</v>
-      </c>
-      <c r="O29" s="187">
+        <v>6567.7808349999996</v>
+      </c>
+      <c r="O29" s="185">
         <f t="shared" si="6"/>
-        <v>195654.98028999998</v>
+        <v>195654.98029000001</v>
       </c>
       <c r="P29" s="7"/>
       <c r="Q29" s="7">
@@ -4990,11 +4985,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F30" s="17">
-        <v>171690.166451</v>
-      </c>
-      <c r="G30" s="179">
+        <v>182441.91668600001</v>
+      </c>
+      <c r="G30" s="177">
         <f>F30</f>
-        <v>171690.166451</v>
+        <v>182441.91668600001</v>
       </c>
       <c r="H30" s="24">
         <f t="shared" si="0"/>
@@ -5018,13 +5013,13 @@
       </c>
       <c r="M30" s="25">
         <f t="shared" si="4"/>
-        <v>99493.969024999999</v>
+        <v>140417.67429700002</v>
       </c>
       <c r="N30" s="25">
         <f t="shared" si="5"/>
-        <v>47047.947661000006</v>
-      </c>
-      <c r="O30" s="187">
+        <v>6124.242389</v>
+      </c>
+      <c r="O30" s="185">
         <f t="shared" si="6"/>
         <v>182441.91668600001</v>
       </c>
@@ -5044,11 +5039,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F31" s="17">
-        <v>197993.67384599999</v>
-      </c>
-      <c r="G31" s="179">
+        <v>210392.62815599999</v>
+      </c>
+      <c r="G31" s="177">
         <f>F31</f>
-        <v>197993.67384599999</v>
+        <v>210392.62815599999</v>
       </c>
       <c r="H31" s="24">
         <f t="shared" si="0"/>
@@ -5072,18 +5067,18 @@
       </c>
       <c r="M31" s="25">
         <f t="shared" si="4"/>
-        <v>114736.77765</v>
+        <v>161930.13136200001</v>
       </c>
       <c r="N31" s="25">
         <f t="shared" si="5"/>
-        <v>54255.850506000002</v>
-      </c>
-      <c r="O31" s="187">
+        <v>7062.4967939999997</v>
+      </c>
+      <c r="O31" s="185">
         <f t="shared" si="6"/>
-        <v>210392.62815599999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="15.6">
+        <v>210392.62815600002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -5097,23 +5092,23 @@
       </c>
       <c r="F32" s="99">
         <f>SUM(F9:F31)</f>
-        <v>15883307.414084934</v>
+        <v>17427160.99127518</v>
       </c>
       <c r="G32" s="99">
         <f>SUM(G9:G31)</f>
-        <v>3936249.2638619998</v>
+        <v>4001448.7106899992</v>
       </c>
       <c r="H32" s="123">
         <f>SUM(H9:H31)</f>
-        <v>11947058.150222933</v>
+        <v>13425712.532139182</v>
       </c>
       <c r="I32" s="54">
         <f>SUM(I9:I31)</f>
-        <v>442041.15155824862</v>
+        <v>496751.36368914973</v>
       </c>
       <c r="J32" s="99">
         <f t="shared" ref="J32" si="8">SUM(J9:J31)</f>
-        <v>0</v>
+        <v>0.25155400001676753</v>
       </c>
       <c r="K32" s="90">
         <f>SUM(K9:K31)</f>
@@ -5122,132 +5117,132 @@
       <c r="L32" s="90"/>
       <c r="M32" s="54">
         <f>SUM(M9:M31)</f>
-        <v>2771419.7500000005</v>
+        <v>3911355.8299999996</v>
       </c>
       <c r="N32" s="90">
         <f>SUM(N9:N31)</f>
-        <v>1256271.9394939998</v>
+        <v>163529.21320600001</v>
       </c>
       <c r="O32" s="54">
         <f>SUM(O9:O31)</f>
-        <v>17416790.99127518</v>
+        <v>18997348.68748033</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:15" hidden="1">
-      <c r="B34" s="231"/>
-      <c r="C34" s="231"/>
-      <c r="D34" s="231"/>
-      <c r="E34" s="231"/>
-      <c r="F34" s="231"/>
-      <c r="G34" s="231"/>
-      <c r="H34" s="231"/>
-      <c r="I34" s="231"/>
-      <c r="J34" s="231"/>
-      <c r="K34" s="231"/>
-      <c r="L34" s="231"/>
-      <c r="M34" s="231"/>
-      <c r="N34" s="231"/>
-      <c r="O34" s="231"/>
+      <c r="B34" s="229"/>
+      <c r="C34" s="229"/>
+      <c r="D34" s="229"/>
+      <c r="E34" s="229"/>
+      <c r="F34" s="229"/>
+      <c r="G34" s="229"/>
+      <c r="H34" s="229"/>
+      <c r="I34" s="229"/>
+      <c r="J34" s="229"/>
+      <c r="K34" s="229"/>
+      <c r="L34" s="229"/>
+      <c r="M34" s="229"/>
+      <c r="N34" s="229"/>
+      <c r="O34" s="229"/>
     </row>
     <row r="35" spans="1:15" hidden="1">
-      <c r="B35" s="231"/>
-      <c r="C35" s="231"/>
-      <c r="D35" s="231"/>
-      <c r="E35" s="231"/>
-      <c r="F35" s="231"/>
-      <c r="G35" s="231"/>
-      <c r="H35" s="231"/>
-      <c r="I35" s="231"/>
-      <c r="J35" s="231"/>
-      <c r="K35" s="231"/>
-      <c r="L35" s="231"/>
-      <c r="M35" s="231"/>
-      <c r="N35" s="231"/>
-      <c r="O35" s="231"/>
+      <c r="B35" s="229"/>
+      <c r="C35" s="229"/>
+      <c r="D35" s="229"/>
+      <c r="E35" s="229"/>
+      <c r="F35" s="229"/>
+      <c r="G35" s="229"/>
+      <c r="H35" s="229"/>
+      <c r="I35" s="229"/>
+      <c r="J35" s="229"/>
+      <c r="K35" s="229"/>
+      <c r="L35" s="229"/>
+      <c r="M35" s="229"/>
+      <c r="N35" s="229"/>
+      <c r="O35" s="229"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
-      <c r="B36" s="231"/>
-      <c r="C36" s="231"/>
-      <c r="D36" s="231"/>
-      <c r="E36" s="231"/>
-      <c r="F36" s="231"/>
-      <c r="G36" s="231"/>
-      <c r="H36" s="231"/>
-      <c r="I36" s="231"/>
-      <c r="J36" s="231"/>
-      <c r="K36" s="231"/>
-      <c r="L36" s="231"/>
-      <c r="M36" s="231"/>
-      <c r="N36" s="231"/>
-      <c r="O36" s="231"/>
+      <c r="B36" s="229"/>
+      <c r="C36" s="229"/>
+      <c r="D36" s="229"/>
+      <c r="E36" s="229"/>
+      <c r="F36" s="229"/>
+      <c r="G36" s="229"/>
+      <c r="H36" s="229"/>
+      <c r="I36" s="229"/>
+      <c r="J36" s="229"/>
+      <c r="K36" s="229"/>
+      <c r="L36" s="229"/>
+      <c r="M36" s="229"/>
+      <c r="N36" s="229"/>
+      <c r="O36" s="229"/>
     </row>
     <row r="37" spans="1:15" hidden="1">
-      <c r="B37" s="231"/>
-      <c r="C37" s="231"/>
-      <c r="D37" s="231"/>
-      <c r="E37" s="231"/>
-      <c r="F37" s="231"/>
-      <c r="G37" s="231"/>
-      <c r="H37" s="231"/>
-      <c r="I37" s="231"/>
-      <c r="J37" s="231"/>
-      <c r="K37" s="231"/>
-      <c r="L37" s="231"/>
-      <c r="M37" s="231"/>
-      <c r="N37" s="231"/>
-      <c r="O37" s="231"/>
+      <c r="B37" s="229"/>
+      <c r="C37" s="229"/>
+      <c r="D37" s="229"/>
+      <c r="E37" s="229"/>
+      <c r="F37" s="229"/>
+      <c r="G37" s="229"/>
+      <c r="H37" s="229"/>
+      <c r="I37" s="229"/>
+      <c r="J37" s="229"/>
+      <c r="K37" s="229"/>
+      <c r="L37" s="229"/>
+      <c r="M37" s="229"/>
+      <c r="N37" s="229"/>
+      <c r="O37" s="229"/>
     </row>
     <row r="38" spans="1:15" hidden="1">
-      <c r="A38" s="233"/>
-      <c r="B38" s="233"/>
-      <c r="C38" s="233"/>
-      <c r="D38" s="233"/>
-      <c r="E38" s="233"/>
-      <c r="F38" s="233"/>
-      <c r="G38" s="233"/>
-      <c r="H38" s="233"/>
-      <c r="I38" s="233"/>
-      <c r="J38" s="233"/>
-      <c r="K38" s="233"/>
-      <c r="L38" s="233"/>
-      <c r="M38" s="233"/>
-      <c r="N38" s="233"/>
-      <c r="O38" s="233"/>
+      <c r="A38" s="231"/>
+      <c r="B38" s="231"/>
+      <c r="C38" s="231"/>
+      <c r="D38" s="231"/>
+      <c r="E38" s="231"/>
+      <c r="F38" s="231"/>
+      <c r="G38" s="231"/>
+      <c r="H38" s="231"/>
+      <c r="I38" s="231"/>
+      <c r="J38" s="231"/>
+      <c r="K38" s="231"/>
+      <c r="L38" s="231"/>
+      <c r="M38" s="231"/>
+      <c r="N38" s="231"/>
+      <c r="O38" s="231"/>
     </row>
     <row r="39" spans="1:15" hidden="1">
-      <c r="A39" s="233"/>
-      <c r="B39" s="233"/>
-      <c r="C39" s="233"/>
-      <c r="D39" s="233"/>
-      <c r="E39" s="233"/>
-      <c r="F39" s="233"/>
-      <c r="G39" s="233"/>
-      <c r="H39" s="233"/>
-      <c r="I39" s="233"/>
-      <c r="J39" s="233"/>
-      <c r="K39" s="233"/>
-      <c r="L39" s="233"/>
-      <c r="M39" s="233"/>
-      <c r="N39" s="233"/>
-      <c r="O39" s="233"/>
+      <c r="A39" s="231"/>
+      <c r="B39" s="231"/>
+      <c r="C39" s="231"/>
+      <c r="D39" s="231"/>
+      <c r="E39" s="231"/>
+      <c r="F39" s="231"/>
+      <c r="G39" s="231"/>
+      <c r="H39" s="231"/>
+      <c r="I39" s="231"/>
+      <c r="J39" s="231"/>
+      <c r="K39" s="231"/>
+      <c r="L39" s="231"/>
+      <c r="M39" s="231"/>
+      <c r="N39" s="231"/>
+      <c r="O39" s="231"/>
     </row>
     <row r="40" spans="1:15" hidden="1">
-      <c r="A40" s="233"/>
-      <c r="B40" s="233"/>
-      <c r="C40" s="233"/>
-      <c r="D40" s="233"/>
-      <c r="E40" s="233"/>
-      <c r="F40" s="233"/>
-      <c r="G40" s="233"/>
-      <c r="H40" s="233"/>
-      <c r="I40" s="233"/>
-      <c r="J40" s="233"/>
-      <c r="K40" s="233"/>
-      <c r="L40" s="233"/>
-      <c r="M40" s="233"/>
-      <c r="N40" s="233"/>
-      <c r="O40" s="233"/>
+      <c r="A40" s="231"/>
+      <c r="B40" s="231"/>
+      <c r="C40" s="231"/>
+      <c r="D40" s="231"/>
+      <c r="E40" s="231"/>
+      <c r="F40" s="231"/>
+      <c r="G40" s="231"/>
+      <c r="H40" s="231"/>
+      <c r="I40" s="231"/>
+      <c r="J40" s="231"/>
+      <c r="K40" s="231"/>
+      <c r="L40" s="231"/>
+      <c r="M40" s="231"/>
+      <c r="N40" s="231"/>
+      <c r="O40" s="231"/>
     </row>
     <row r="41" spans="1:15">
       <c r="O41" s="7"/>
@@ -5272,25 +5267,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.109375" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="240" t="s">
+      <c r="A1" s="238" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="241"/>
-      <c r="E1" s="241"/>
-      <c r="F1" s="241"/>
-      <c r="G1" s="242"/>
+      <c r="B1" s="239"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="240"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>
@@ -5326,13 +5321,13 @@
       <c r="C6" s="16"/>
       <c r="G6" s="31"/>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1">
       <c r="A7" s="62"/>
       <c r="B7" s="32"/>
       <c r="C7" s="16"/>
       <c r="G7" s="31"/>
     </row>
-    <row r="8" spans="1:7" ht="29.4" thickBot="1">
+    <row r="8" spans="1:7" ht="30.75" thickBot="1">
       <c r="A8" s="26" t="s">
         <v>0</v>
       </c>
@@ -5693,7 +5688,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6">
+    <row r="24" spans="1:7" ht="15.75">
       <c r="A24" s="51">
         <v>16</v>
       </c>
@@ -5715,7 +5710,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.6">
+    <row r="25" spans="1:7" ht="15.75">
       <c r="A25" s="51">
         <v>17</v>
       </c>
@@ -5737,7 +5732,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.6">
+    <row r="26" spans="1:7" ht="15.75">
       <c r="A26" s="51">
         <v>18</v>
       </c>
@@ -5759,7 +5754,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.6">
+    <row r="27" spans="1:7" ht="15.75">
       <c r="A27" s="51">
         <v>19</v>
       </c>
@@ -5785,7 +5780,7 @@
         <v>17603.28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.6">
+    <row r="28" spans="1:7" ht="15.75">
       <c r="A28" s="51">
         <v>20</v>
       </c>
@@ -5807,7 +5802,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.6">
+    <row r="29" spans="1:7" ht="15.75">
       <c r="A29" s="51">
         <v>21</v>
       </c>
@@ -5829,7 +5824,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.6">
+    <row r="30" spans="1:7" ht="15.75">
       <c r="A30" s="51">
         <v>22</v>
       </c>
@@ -5851,7 +5846,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.6">
+    <row r="31" spans="1:7" ht="15.75">
       <c r="A31" s="51">
         <v>23</v>
       </c>
@@ -5873,7 +5868,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.6">
+    <row r="32" spans="1:7" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
